--- a/sbom_output/public/sbom_report.xlsx
+++ b/sbom_output/public/sbom_report.xlsx
@@ -71,13 +71,13 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -156,8 +156,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC107"/>
-        <bgColor rgb="00FFC107"/>
+        <fgColor rgb="004CAF50"/>
+        <bgColor rgb="004CAF50"/>
       </patternFill>
     </fill>
     <fill>
@@ -170,6 +170,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FF4C4C"/>
         <bgColor rgb="00FF4C4C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC107"/>
+        <bgColor rgb="00FFC107"/>
       </patternFill>
     </fill>
     <fill>
@@ -194,12 +200,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFCDD2"/>
         <bgColor rgb="00FFCDD2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004CAF50"/>
-        <bgColor rgb="004CAF50"/>
       </patternFill>
     </fill>
   </fills>
@@ -229,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -296,10 +296,13 @@
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -309,13 +312,13 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -325,13 +328,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -723,7 +726,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CycloneDX v1.7 | Generated: 2026-06-26T06:14:55Z | Report Date: 2026-06-26 11:44</t>
+          <t>CycloneDX v1.7 | Generated: 2026-06-26T09:25:48Z | Report Date: 2026-06-26 14:55</t>
         </is>
       </c>
     </row>
@@ -756,12 +759,12 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -868,7 +871,7 @@
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -938,7 +941,7 @@
       </c>
       <c r="E11" s="21" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -971,7 +974,7 @@
           <t>Apache-2.0</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -1006,7 +1009,7 @@
           <t>Apache-2.0</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1041,7 +1044,7 @@
           <t>Apache-2.0</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1073,7 +1076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1090,27 +1093,34 @@
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="45" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="45" customWidth="1" min="16" max="16"/>
+    <col width="45" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
     <col width="45" customWidth="1" min="17" max="17"/>
-    <col width="23" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
-    <col width="34" customWidth="1" min="22" max="22"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="37" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="45" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="45" customWidth="1" min="28" max="28"/>
+    <col width="23" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>SBOM Component Data - All 21 Client Attributes</t>
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>SBOM Component Data - All 21 Client Attributes + Enterprise Enhancements</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Author: Compliance &amp; Enrichment Specialist (Team Member 3)  |  Generated: 2026-06-26T06:14:55Z</t>
+          <t>Author: Compliance &amp; Enrichment Specialist (Team Member 3)  |  Generated: 2026-06-26T09:25:48Z</t>
         </is>
       </c>
     </row>
@@ -1183,47 +1193,82 @@
       </c>
       <c r="N4" s="18" t="inlineStr">
         <is>
+          <t>Criticality Reason</t>
+        </is>
+      </c>
+      <c r="O4" s="18" t="inlineStr">
+        <is>
           <t>Usage Restrictions</t>
         </is>
       </c>
-      <c r="O4" s="18" t="inlineStr">
+      <c r="P4" s="18" t="inlineStr">
         <is>
           <t>Checksums or Hashes</t>
         </is>
       </c>
-      <c r="P4" s="18" t="inlineStr">
+      <c r="Q4" s="18" t="inlineStr">
         <is>
           <t>Comments or Notes</t>
         </is>
       </c>
-      <c r="Q4" s="18" t="inlineStr">
+      <c r="R4" s="18" t="inlineStr">
         <is>
           <t>Author of SBOM Data</t>
         </is>
       </c>
-      <c r="R4" s="18" t="inlineStr">
+      <c r="S4" s="18" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="S4" s="18" t="inlineStr">
+      <c r="T4" s="18" t="inlineStr">
         <is>
           <t>Executable Property</t>
         </is>
       </c>
-      <c r="T4" s="18" t="inlineStr">
+      <c r="U4" s="18" t="inlineStr">
+        <is>
+          <t>Executable Evidence</t>
+        </is>
+      </c>
+      <c r="V4" s="18" t="inlineStr">
         <is>
           <t>Archive Property</t>
         </is>
       </c>
-      <c r="U4" s="18" t="inlineStr">
+      <c r="W4" s="18" t="inlineStr">
         <is>
           <t>Structured Property</t>
         </is>
       </c>
-      <c r="V4" s="18" t="inlineStr">
+      <c r="X4" s="18" t="inlineStr">
         <is>
           <t>Unique Identifier (PURL)</t>
+        </is>
+      </c>
+      <c r="Y4" s="18" t="inlineStr">
+        <is>
+          <t>Trust Score</t>
+        </is>
+      </c>
+      <c r="Z4" s="18" t="inlineStr">
+        <is>
+          <t>Trust Score Reasons</t>
+        </is>
+      </c>
+      <c r="AA4" s="18" t="inlineStr">
+        <is>
+          <t>Repository Registry</t>
+        </is>
+      </c>
+      <c r="AB4" s="18" t="inlineStr">
+        <is>
+          <t>Repository URL</t>
+        </is>
+      </c>
+      <c r="AC4" s="18" t="inlineStr">
+        <is>
+          <t>Repository Ecosystem</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1276,7 @@
       <c r="A5" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>requirements.txt</t>
         </is>
@@ -1278,62 +1323,99 @@
       </c>
       <c r="K5" s="19" t="inlineStr">
         <is>
-          <t>2026-06-26T06:14:56.141587Z</t>
+          <t>2026-06-26T09:25:49.183802Z</t>
         </is>
       </c>
       <c r="L5" s="19" t="inlineStr">
         <is>
-          <t>2029-06-25T06:14:56Z</t>
+          <t>2029-06-25T09:25:49Z</t>
         </is>
       </c>
       <c r="M5" s="21" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="N5" s="20" t="inlineStr">
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N5" s="19" t="inlineStr">
+        <is>
+          <t>Score 15: component type='application' (+15)</t>
+        </is>
+      </c>
+      <c r="O5" s="20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O5" s="20" t="inlineStr">
+      <c r="P5" s="20" t="inlineStr">
         <is>
           <t>SHA-256:5a1746a9ad87d418...</t>
         </is>
       </c>
-      <c r="P5" s="20" t="inlineStr">
+      <c r="Q5" s="20" t="inlineStr">
         <is>
           <t>Scanned and verified library</t>
         </is>
       </c>
-      <c r="Q5" s="19" t="inlineStr">
+      <c r="R5" s="19" t="inlineStr">
         <is>
           <t>Compliance &amp; Enrichment Specialist (Team Member 3)</t>
         </is>
       </c>
-      <c r="R5" s="19" t="inlineStr">
-        <is>
-          <t>2026-06-26T06:14:55Z</t>
-        </is>
-      </c>
-      <c r="S5" s="19" t="inlineStr">
+      <c r="S5" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-26T09:25:48Z</t>
+        </is>
+      </c>
+      <c r="T5" s="20" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="T5" s="19" t="inlineStr">
+      <c r="U5" s="19" t="inlineStr">
+        <is>
+          <t>CycloneDX type=application</t>
+        </is>
+      </c>
+      <c r="V5" s="19" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="U5" s="20" t="inlineStr">
+      <c r="W5" s="20" t="inlineStr">
         <is>
           <t>CycloneDX JSON v1.6</t>
         </is>
       </c>
-      <c r="V5" s="20" t="inlineStr">
+      <c r="X5" s="19" t="inlineStr">
         <is>
           <t>pkg:pypi/requirements.txt@1.0.0</t>
+        </is>
+      </c>
+      <c r="Y5" s="20" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Z5" s="20" t="inlineStr">
+        <is>
+          <t>+25: Hash/checksum verified
++20: PURL identifier available
++15: License identified (Apache-2.0)</t>
+        </is>
+      </c>
+      <c r="AA5" s="20" t="inlineStr">
+        <is>
+          <t>PyPI</t>
+        </is>
+      </c>
+      <c r="AB5" s="20" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/requirements.txt/</t>
+        </is>
+      </c>
+      <c r="AC5" s="20" t="inlineStr">
+        <is>
+          <t>Python</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1423,7 @@
       <c r="A6" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>django</t>
         </is>
@@ -1401,49 +1483,88 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="N6" s="23" t="inlineStr">
+      <c r="N6" s="22" t="inlineStr">
+        <is>
+          <t>Manually overridden in config to 'critical'</t>
+        </is>
+      </c>
+      <c r="O6" s="23" t="inlineStr">
         <is>
           <t>Subject to internal framework deployment guidelines</t>
         </is>
       </c>
-      <c r="O6" s="23" t="inlineStr">
+      <c r="P6" s="23" t="inlineStr">
         <is>
           <t>SHA-256:6a47faad96b2260a...</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="Q6" s="23" t="inlineStr">
         <is>
           <t>Primary web backend framework</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="R6" s="22" t="inlineStr">
         <is>
           <t>Compliance &amp; Enrichment Specialist (Team Member 3)</t>
         </is>
       </c>
-      <c r="R6" s="22" t="inlineStr">
-        <is>
-          <t>2026-06-26T06:14:55Z</t>
-        </is>
-      </c>
-      <c r="S6" s="22" t="inlineStr">
+      <c r="S6" s="23" t="inlineStr">
+        <is>
+          <t>2026-06-26T09:25:48Z</t>
+        </is>
+      </c>
+      <c r="T6" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="T6" s="22" t="inlineStr">
+      <c r="U6" s="22" t="inlineStr">
+        <is>
+          <t>PyPI package (typically a library)</t>
+        </is>
+      </c>
+      <c r="V6" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="U6" s="23" t="inlineStr">
+      <c r="W6" s="23" t="inlineStr">
         <is>
           <t>CycloneDX JSON v1.6</t>
         </is>
       </c>
-      <c r="V6" s="23" t="inlineStr">
+      <c r="X6" s="22" t="inlineStr">
         <is>
           <t>pkg:pypi/django@2.1</t>
+        </is>
+      </c>
+      <c r="Y6" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z6" s="23" t="inlineStr">
+        <is>
+          <t>+30: Version confirmed from package registry (API available)
++25: Hash/checksum verified
++20: PURL identifier available
++15: License identified (Apache-2.0)
++10: Manually reviewed in config overrides</t>
+        </is>
+      </c>
+      <c r="AA6" s="23" t="inlineStr">
+        <is>
+          <t>PyPI</t>
+        </is>
+      </c>
+      <c r="AB6" s="23" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/django/</t>
+        </is>
+      </c>
+      <c r="AC6" s="23" t="inlineStr">
+        <is>
+          <t>Python</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1572,7 @@
       <c r="A7" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>jinja2</t>
         </is>
@@ -1508,52 +1629,90 @@
       </c>
       <c r="M7" s="21" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="N7" s="20" t="inlineStr">
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N7" s="19" t="inlineStr">
+        <is>
+          <t>Score 10: component type='library' (+10)</t>
+        </is>
+      </c>
+      <c r="O7" s="20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O7" s="20" t="inlineStr">
+      <c r="P7" s="20" t="inlineStr">
         <is>
           <t>SHA-256:bea121f34d38d518...</t>
         </is>
       </c>
-      <c r="P7" s="20" t="inlineStr">
+      <c r="Q7" s="20" t="inlineStr">
         <is>
           <t>Scanned and verified library</t>
         </is>
       </c>
-      <c r="Q7" s="19" t="inlineStr">
+      <c r="R7" s="19" t="inlineStr">
         <is>
           <t>Compliance &amp; Enrichment Specialist (Team Member 3)</t>
         </is>
       </c>
-      <c r="R7" s="19" t="inlineStr">
-        <is>
-          <t>2026-06-26T06:14:55Z</t>
-        </is>
-      </c>
-      <c r="S7" s="19" t="inlineStr">
+      <c r="S7" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-26T09:25:48Z</t>
+        </is>
+      </c>
+      <c r="T7" s="20" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="T7" s="19" t="inlineStr">
+      <c r="U7" s="19" t="inlineStr">
+        <is>
+          <t>PyPI package (typically a library)</t>
+        </is>
+      </c>
+      <c r="V7" s="19" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="U7" s="20" t="inlineStr">
+      <c r="W7" s="20" t="inlineStr">
         <is>
           <t>CycloneDX JSON v1.6</t>
         </is>
       </c>
-      <c r="V7" s="20" t="inlineStr">
+      <c r="X7" s="19" t="inlineStr">
         <is>
           <t>pkg:pypi/jinja2@2.10</t>
+        </is>
+      </c>
+      <c r="Y7" s="20" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="Z7" s="20" t="inlineStr">
+        <is>
+          <t>+30: Version confirmed from package registry (API available)
++25: Hash/checksum verified
++20: PURL identifier available
++15: License identified (Apache-2.0)</t>
+        </is>
+      </c>
+      <c r="AA7" s="20" t="inlineStr">
+        <is>
+          <t>PyPI</t>
+        </is>
+      </c>
+      <c r="AB7" s="20" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/jinja2/</t>
+        </is>
+      </c>
+      <c r="AC7" s="20" t="inlineStr">
+        <is>
+          <t>Python</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1720,7 @@
       <c r="A8" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>numpy</t>
         </is>
@@ -1616,54 +1775,93 @@
           <t>2021-07-22T16:03:25Z</t>
         </is>
       </c>
-      <c r="M8" s="21" t="inlineStr">
+      <c r="M8" s="25" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="N8" s="23" t="inlineStr">
+      <c r="N8" s="22" t="inlineStr">
+        <is>
+          <t>Manually overridden in config to 'medium'</t>
+        </is>
+      </c>
+      <c r="O8" s="23" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O8" s="23" t="inlineStr">
+      <c r="P8" s="23" t="inlineStr">
         <is>
           <t>SHA-256:a890e78aadf77316...</t>
         </is>
       </c>
-      <c r="P8" s="23" t="inlineStr">
+      <c r="Q8" s="23" t="inlineStr">
         <is>
           <t>Numeric and mathematical computation core package</t>
         </is>
       </c>
-      <c r="Q8" s="22" t="inlineStr">
+      <c r="R8" s="22" t="inlineStr">
         <is>
           <t>Compliance &amp; Enrichment Specialist (Team Member 3)</t>
         </is>
       </c>
-      <c r="R8" s="22" t="inlineStr">
-        <is>
-          <t>2026-06-26T06:14:55Z</t>
-        </is>
-      </c>
-      <c r="S8" s="22" t="inlineStr">
+      <c r="S8" s="23" t="inlineStr">
+        <is>
+          <t>2026-06-26T09:25:48Z</t>
+        </is>
+      </c>
+      <c r="T8" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="T8" s="22" t="inlineStr">
+      <c r="U8" s="22" t="inlineStr">
+        <is>
+          <t>PyPI package (typically a library)</t>
+        </is>
+      </c>
+      <c r="V8" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="U8" s="23" t="inlineStr">
+      <c r="W8" s="23" t="inlineStr">
         <is>
           <t>CycloneDX JSON v1.6</t>
         </is>
       </c>
-      <c r="V8" s="23" t="inlineStr">
+      <c r="X8" s="22" t="inlineStr">
         <is>
           <t>pkg:pypi/numpy@1.15.0</t>
+        </is>
+      </c>
+      <c r="Y8" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z8" s="23" t="inlineStr">
+        <is>
+          <t>+30: Version confirmed from package registry (API available)
++25: Hash/checksum verified
++20: PURL identifier available
++15: License identified (Apache-2.0)
++10: Manually reviewed in config overrides</t>
+        </is>
+      </c>
+      <c r="AA8" s="23" t="inlineStr">
+        <is>
+          <t>PyPI</t>
+        </is>
+      </c>
+      <c r="AB8" s="23" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/numpy/</t>
+        </is>
+      </c>
+      <c r="AC8" s="23" t="inlineStr">
+        <is>
+          <t>Python</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1869,7 @@
       <c r="A9" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>requests</t>
         </is>
@@ -1726,54 +1924,93 @@
           <t>2021-10-17T15:46:10Z</t>
         </is>
       </c>
-      <c r="M9" s="25" t="inlineStr">
+      <c r="M9" s="26" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr">
+      <c r="N9" s="19" t="inlineStr">
+        <is>
+          <t>Manually overridden in config to 'high'</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O9" s="20" t="inlineStr">
+      <c r="P9" s="20" t="inlineStr">
         <is>
           <t>SHA-256:29a9bb27fe60f047...</t>
         </is>
       </c>
-      <c r="P9" s="20" t="inlineStr">
+      <c r="Q9" s="20" t="inlineStr">
         <is>
           <t>Critical HTTP client library used for core backend integrations</t>
         </is>
       </c>
-      <c r="Q9" s="19" t="inlineStr">
+      <c r="R9" s="19" t="inlineStr">
         <is>
           <t>Compliance &amp; Enrichment Specialist (Team Member 3)</t>
         </is>
       </c>
-      <c r="R9" s="19" t="inlineStr">
-        <is>
-          <t>2026-06-26T06:14:55Z</t>
-        </is>
-      </c>
-      <c r="S9" s="19" t="inlineStr">
+      <c r="S9" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-26T09:25:48Z</t>
+        </is>
+      </c>
+      <c r="T9" s="20" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="T9" s="19" t="inlineStr">
+      <c r="U9" s="19" t="inlineStr">
+        <is>
+          <t>PyPI package (typically a library)</t>
+        </is>
+      </c>
+      <c r="V9" s="19" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="U9" s="20" t="inlineStr">
+      <c r="W9" s="20" t="inlineStr">
         <is>
           <t>CycloneDX JSON v1.6</t>
         </is>
       </c>
-      <c r="V9" s="20" t="inlineStr">
+      <c r="X9" s="19" t="inlineStr">
         <is>
           <t>pkg:pypi/requests@2.20.0</t>
+        </is>
+      </c>
+      <c r="Y9" s="20" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z9" s="20" t="inlineStr">
+        <is>
+          <t>+30: Version confirmed from package registry (API available)
++25: Hash/checksum verified
++20: PURL identifier available
++15: License identified (Apache-2.0)
++10: Manually reviewed in config overrides</t>
+        </is>
+      </c>
+      <c r="AA9" s="20" t="inlineStr">
+        <is>
+          <t>PyPI</t>
+        </is>
+      </c>
+      <c r="AB9" s="20" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/requests/</t>
+        </is>
+      </c>
+      <c r="AC9" s="20" t="inlineStr">
+        <is>
+          <t>Python</t>
         </is>
       </c>
     </row>
@@ -1781,7 +2018,7 @@
       <c r="A10" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>urllib3</t>
         </is>
@@ -1836,61 +2073,100 @@
           <t>2022-04-16T17:49:45Z</t>
         </is>
       </c>
-      <c r="M10" s="25" t="inlineStr">
+      <c r="M10" s="26" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="N10" s="23" t="inlineStr">
+      <c r="N10" s="22" t="inlineStr">
+        <is>
+          <t>Manually overridden in config to 'high'</t>
+        </is>
+      </c>
+      <c r="O10" s="23" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O10" s="23" t="inlineStr">
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t>SHA-256:889a9b94b6891674...</t>
         </is>
       </c>
-      <c r="P10" s="23" t="inlineStr">
+      <c r="Q10" s="23" t="inlineStr">
         <is>
           <t>Core networking transport library for HTTP calls</t>
         </is>
       </c>
-      <c r="Q10" s="22" t="inlineStr">
+      <c r="R10" s="22" t="inlineStr">
         <is>
           <t>Compliance &amp; Enrichment Specialist (Team Member 3)</t>
         </is>
       </c>
-      <c r="R10" s="22" t="inlineStr">
-        <is>
-          <t>2026-06-26T06:14:55Z</t>
-        </is>
-      </c>
-      <c r="S10" s="22" t="inlineStr">
+      <c r="S10" s="23" t="inlineStr">
+        <is>
+          <t>2026-06-26T09:25:48Z</t>
+        </is>
+      </c>
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="T10" s="22" t="inlineStr">
+      <c r="U10" s="22" t="inlineStr">
+        <is>
+          <t>PyPI package (typically a library)</t>
+        </is>
+      </c>
+      <c r="V10" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="U10" s="23" t="inlineStr">
+      <c r="W10" s="23" t="inlineStr">
         <is>
           <t>CycloneDX JSON v1.6</t>
         </is>
       </c>
-      <c r="V10" s="23" t="inlineStr">
+      <c r="X10" s="22" t="inlineStr">
         <is>
           <t>pkg:pypi/urllib3@1.24.2</t>
+        </is>
+      </c>
+      <c r="Y10" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z10" s="23" t="inlineStr">
+        <is>
+          <t>+30: Version confirmed from package registry (API available)
++25: Hash/checksum verified
++20: PURL identifier available
++15: License identified (Apache-2.0)
++10: Manually reviewed in config overrides</t>
+        </is>
+      </c>
+      <c r="AA10" s="23" t="inlineStr">
+        <is>
+          <t>PyPI</t>
+        </is>
+      </c>
+      <c r="AB10" s="23" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/urllib3/</t>
+        </is>
+      </c>
+      <c r="AC10" s="23" t="inlineStr">
+        <is>
+          <t>Python</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:V2"/>
-    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:AC2"/>
+    <mergeCell ref="A1:AC1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1917,7 +2193,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Vulnerability Matrix</t>
         </is>
@@ -1975,7 +2251,7 @@
           <t>CVE-2018-16984</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2015,7 +2291,7 @@
           <t>CVE-2019-10906</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2055,7 +2331,7 @@
           <t>CVE-2019-11236</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2095,7 +2371,7 @@
           <t>CVE-2019-11358</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2135,7 +2411,7 @@
           <t>CVE-2019-12308</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2175,7 +2451,7 @@
           <t>CVE-2019-12781</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2215,7 +2491,7 @@
           <t>CVE-2019-14232</t>
         </is>
       </c>
-      <c r="C10" s="30" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2255,7 +2531,7 @@
           <t>CVE-2019-14233</t>
         </is>
       </c>
-      <c r="C11" s="30" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2295,7 +2571,7 @@
           <t>CVE-2019-14234</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -2335,7 +2611,7 @@
           <t>CVE-2019-14235</t>
         </is>
       </c>
-      <c r="C13" s="30" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2375,7 +2651,7 @@
           <t>CVE-2019-19118</t>
         </is>
       </c>
-      <c r="C14" s="30" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2415,7 +2691,7 @@
           <t>CVE-2019-19844</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -2455,7 +2731,7 @@
           <t>CVE-2019-3498</t>
         </is>
       </c>
-      <c r="C16" s="30" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2495,7 +2771,7 @@
           <t>CVE-2019-6446</t>
         </is>
       </c>
-      <c r="C17" s="29" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2535,7 +2811,7 @@
           <t>CVE-2019-6975</t>
         </is>
       </c>
-      <c r="C18" s="30" t="inlineStr">
+      <c r="C18" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2575,7 +2851,7 @@
           <t>CVE-2020-26137</t>
         </is>
       </c>
-      <c r="C19" s="29" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2615,7 +2891,7 @@
           <t>CVE-2020-28493</t>
         </is>
       </c>
-      <c r="C20" s="29" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2655,7 +2931,7 @@
           <t>CVE-2020-7471</t>
         </is>
       </c>
-      <c r="C21" s="31" t="inlineStr">
+      <c r="C21" s="32" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -2695,7 +2971,7 @@
           <t>CVE-2021-33203</t>
         </is>
       </c>
-      <c r="C22" s="29" t="inlineStr">
+      <c r="C22" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2735,7 +3011,7 @@
           <t>CVE-2021-33430</t>
         </is>
       </c>
-      <c r="C23" s="29" t="inlineStr">
+      <c r="C23" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2775,7 +3051,7 @@
           <t>CVE-2021-34141</t>
         </is>
       </c>
-      <c r="C24" s="29" t="inlineStr">
+      <c r="C24" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2815,7 +3091,7 @@
           <t>CVE-2021-41495</t>
         </is>
       </c>
-      <c r="C25" s="29" t="inlineStr">
+      <c r="C25" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2855,7 +3131,7 @@
           <t>CVE-2021-41496</t>
         </is>
       </c>
-      <c r="C26" s="29" t="inlineStr">
+      <c r="C26" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2895,7 +3171,7 @@
           <t>CVE-2022-36359</t>
         </is>
       </c>
-      <c r="C27" s="30" t="inlineStr">
+      <c r="C27" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2935,7 +3211,7 @@
           <t>CVE-2023-32681</t>
         </is>
       </c>
-      <c r="C28" s="29" t="inlineStr">
+      <c r="C28" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2975,7 +3251,7 @@
           <t>CVE-2023-43804</t>
         </is>
       </c>
-      <c r="C29" s="29" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -3015,7 +3291,7 @@
           <t>CVE-2023-45803</t>
         </is>
       </c>
-      <c r="C30" s="29" t="inlineStr">
+      <c r="C30" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -3055,7 +3331,7 @@
           <t>CVE-2024-22195</t>
         </is>
       </c>
-      <c r="C31" s="29" t="inlineStr">
+      <c r="C31" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -3095,7 +3371,7 @@
           <t>CVE-2024-34064</t>
         </is>
       </c>
-      <c r="C32" s="29" t="inlineStr">
+      <c r="C32" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -3135,7 +3411,7 @@
           <t>CVE-2024-35195</t>
         </is>
       </c>
-      <c r="C33" s="29" t="inlineStr">
+      <c r="C33" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -3175,7 +3451,7 @@
           <t>CVE-2024-37891</t>
         </is>
       </c>
-      <c r="C34" s="29" t="inlineStr">
+      <c r="C34" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -3215,7 +3491,7 @@
           <t>CVE-2024-45231</t>
         </is>
       </c>
-      <c r="C35" s="29" t="inlineStr">
+      <c r="C35" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -3255,7 +3531,7 @@
           <t>CVE-2024-47081</t>
         </is>
       </c>
-      <c r="C36" s="29" t="inlineStr">
+      <c r="C36" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -3295,7 +3571,7 @@
           <t>CVE-2024-56326</t>
         </is>
       </c>
-      <c r="C37" s="30" t="inlineStr">
+      <c r="C37" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3335,7 +3611,7 @@
           <t>CVE-2025-27516</t>
         </is>
       </c>
-      <c r="C38" s="30" t="inlineStr">
+      <c r="C38" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3375,7 +3651,7 @@
           <t>CVE-2025-48432</t>
         </is>
       </c>
-      <c r="C39" s="29" t="inlineStr">
+      <c r="C39" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -3415,7 +3691,7 @@
           <t>CVE-2025-50181</t>
         </is>
       </c>
-      <c r="C40" s="29" t="inlineStr">
+      <c r="C40" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -3455,7 +3731,7 @@
           <t>CVE-2025-57833</t>
         </is>
       </c>
-      <c r="C41" s="30" t="inlineStr">
+      <c r="C41" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3495,7 +3771,7 @@
           <t>CVE-2025-64458</t>
         </is>
       </c>
-      <c r="C42" s="30" t="inlineStr">
+      <c r="C42" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3536,7 +3812,7 @@
           <t>CVE-2025-64459</t>
         </is>
       </c>
-      <c r="C43" s="31" t="inlineStr">
+      <c r="C43" s="32" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -3577,7 +3853,7 @@
           <t>CVE-2025-66418</t>
         </is>
       </c>
-      <c r="C44" s="30" t="inlineStr">
+      <c r="C44" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3617,7 +3893,7 @@
           <t>CVE-2025-66471</t>
         </is>
       </c>
-      <c r="C45" s="30" t="inlineStr">
+      <c r="C45" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3657,7 +3933,7 @@
           <t>CVE-2026-21441</t>
         </is>
       </c>
-      <c r="C46" s="30" t="inlineStr">
+      <c r="C46" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3697,7 +3973,7 @@
           <t>CVE-2026-25645</t>
         </is>
       </c>
-      <c r="C47" s="29" t="inlineStr">
+      <c r="C47" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -3737,7 +4013,7 @@
           <t>CVE-2026-44431</t>
         </is>
       </c>
-      <c r="C48" s="30" t="inlineStr">
+      <c r="C48" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3793,69 +4069,69 @@
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Report Legend &amp; Attribute Definitions</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>Criticality Levels</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>Core component; failure causes system-wide outage or critical security breach.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Important component; failure significantly impacts functionality or security.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Standard component; moderate impact on operations.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Minor or utility component; minimal operational impact.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>21 Client-Required SBOM Attributes</t>
         </is>

--- a/sbom_output/public/sbom_report.xlsx
+++ b/sbom_output/public/sbom_report.xlsx
@@ -156,20 +156,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004CAF50"/>
-        <bgColor rgb="004CAF50"/>
+        <fgColor rgb="00FF4C4C"/>
+        <bgColor rgb="00FF4C4C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4F6F9"/>
         <bgColor rgb="00F4F6F9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF4C4C"/>
-        <bgColor rgb="00FF4C4C"/>
       </patternFill>
     </fill>
     <fill>
@@ -186,14 +180,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
-        <bgColor rgb="00FFF9C4"/>
+        <fgColor rgb="004CAF50"/>
+        <bgColor rgb="004CAF50"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE0B2"/>
         <bgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9C4"/>
+        <bgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -296,13 +296,13 @@
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -322,19 +322,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -726,7 +726,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CycloneDX v1.7 | Generated: 2026-06-26T09:25:48Z | Report Date: 2026-06-26 14:55</t>
+          <t>CycloneDX v1.5 | Generated: 2026-06-29T08:32:21Z | Report Date: 2026-06-29 14:02</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>requirements.txt</t>
+          <t>django</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>1.0.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>GHSA-337x-4q8g-prc5, GHSA-68w8-qjq3-2gfm, GHSA-6c3j-c64m-qhgq, GHSA-6c7v-2f49-8h26, GHSA-6mx3-3vqg-hpp2, GHSA-6r97-cj55-9hrq, GHSA-6w2r-r2m5-xq5w, GHSA-7rp2-fm2h-wchj, GHSA-7xr5-9hcq-chf9, GHSA-8x94-hmjh-97hq, GHSA-c4qh-4vgv-qc6g, GHSA-frmv-pr5f-9mcr, GHSA-h5jv-4p7w-64jg, GHSA-hmr4-m2h5-33qx, GHSA-hvmf-r92r-27hr, GHSA-qw25-v68c-qjf3, GHSA-rrqc-c2jx-6jgv, GHSA-v9qg-3j8p-r63v, GHSA-vfq6-hq5r-27r6, GHSA-wh4h-v3f2-r2pp, CVE-2018-16984, CVE-2019-11358, CVE-2019-12308, CVE-2019-12781, CVE-2019-14232, CVE-2019-14233, CVE-2019-14234, CVE-2019-14235, CVE-2019-19118, CVE-2019-19844, CVE-2019-3498, CVE-2019-6975, CVE-2020-7471, CVE-2021-33203, CVE-2022-36359, CVE-2024-45231, CVE-2025-48432, CVE-2025-57833, CVE-2025-64458, CVE-2025-64459</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
         <is>
-          <t>pkg:pypi/requirements.txt@1.0.0</t>
+          <t>pkg:pypi/django@2.1</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>django</t>
+          <t>jinja2</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -906,17 +906,17 @@
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>CVE-2018-16984, CVE-2019-11358, CVE-2019-12308, CVE-2019-12781, CVE-2019-14232, CVE-2019-14233, CVE-2019-14234, CVE-2019-14235, CVE-2019-19118, CVE-2019-19844, CVE-2019-3498, CVE-2019-6975, CVE-2020-7471, CVE-2021-33203, CVE-2022-36359, CVE-2024-45231, CVE-2025-48432, CVE-2025-57833, CVE-2025-64458, CVE-2025-64459</t>
+          <t>GHSA-462w-v97r-4m45, GHSA-cpwx-vrp4-4pq7, GHSA-g3rq-g295-4j3m, GHSA-h5c8-rqwp-cp95, GHSA-h75v-3vvj-5mfj, GHSA-q2x7-8rv6-6q7h, CVE-2019-10906, CVE-2020-28493, CVE-2024-22195, CVE-2024-34064, CVE-2024-56326, CVE-2025-27516</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>pkg:pypi/django@2.1</t>
+          <t>pkg:pypi/jinja2@2.10</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>jinja2</t>
+          <t>numpy</t>
         </is>
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.15.0</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -939,19 +939,19 @@
           <t>Apache-2.0</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>CVE-2019-10906, CVE-2020-28493, CVE-2024-22195, CVE-2024-34064, CVE-2024-56326, CVE-2025-27516</t>
+          <t>GHSA-5545-2q6w-2gh6, GHSA-6p56-wp2h-9hxr, GHSA-9fq2-x9r6-wfmf, GHSA-f7c7-j99h-c22f, GHSA-fpfv-jqm9-f5jm, CVE-2019-6446, CVE-2021-33430, CVE-2021-34141, CVE-2021-41495, CVE-2021-41496</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>pkg:pypi/jinja2@2.10</t>
+          <t>pkg:pypi/numpy@1.15.0</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>numpy</t>
+          <t>requests</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>1.15.0</t>
+          <t>2.20.0</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="E12" s="25" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>CVE-2019-6446, CVE-2021-33430, CVE-2021-34141, CVE-2021-41495, CVE-2021-41496</t>
+          <t>GHSA-9hjg-9r4m-mvj7, GHSA-9wx4-h78v-vm56, GHSA-j8r2-6x86-q33q, CVE-2023-32681, CVE-2024-35195, CVE-2024-47081, CVE-2026-25645</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>pkg:pypi/numpy@1.15.0</t>
+          <t>pkg:pypi/requests@2.20.0</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>requests</t>
+          <t>urllib3</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>2.20.0</t>
+          <t>1.24.2</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -1009,19 +1009,19 @@
           <t>Apache-2.0</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>CVE-2023-32681, CVE-2024-35195, CVE-2024-47081, CVE-2026-25645</t>
+          <t>GHSA-2xpw-w6gg-jr37, GHSA-34jh-p97f-mpxf, GHSA-38jv-5279-wg99, GHSA-g4mx-q9vg-27p4, GHSA-gm62-xv2j-4w53, GHSA-pq67-6m6q-mj2v, GHSA-r64q-w8jr-g9qp, GHSA-v845-jxx5-vc9f, GHSA-wqvq-5m8c-6g24, CVE-2019-11236, CVE-2020-26137, CVE-2023-43804, CVE-2023-45803, CVE-2024-37891, CVE-2025-50181, CVE-2025-66418, CVE-2025-66471, CVE-2026-21441, CVE-2026-44431</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>pkg:pypi/requests@2.20.0</t>
+          <t>pkg:pypi/urllib3@1.24.2</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>urllib3</t>
+          <t>requirements.txt</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>1.24.2</t>
+          <t>1.0.0</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E14" s="26" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>CVE-2019-11236, CVE-2020-26137, CVE-2023-43804, CVE-2023-45803, CVE-2024-37891, CVE-2025-50181, CVE-2025-66418, CVE-2025-66471, CVE-2026-21441, CVE-2026-44431</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>pkg:pypi/urllib3@1.24.2</t>
+          <t>pkg:pypi/requirements.txt@1.0.0</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
     <col width="45" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
     <col width="45" customWidth="1" min="17" max="17"/>
-    <col width="45" customWidth="1" min="18" max="18"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
     <col width="23" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
     <col width="37" customWidth="1" min="21" max="21"/>
     <col width="19" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="31" customWidth="1" min="23" max="23"/>
     <col width="34" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="45" customWidth="1" min="26" max="26"/>
@@ -1120,7 +1120,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Author: Compliance &amp; Enrichment Specialist (Team Member 3)  |  Generated: 2026-06-26T09:25:48Z</t>
+          <t>Author: Client-Assigned Scanning Service  |  Generated: 2026-06-29T08:32:21Z</t>
         </is>
       </c>
     </row>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="B5" s="28" t="inlineStr">
         <is>
-          <t>requirements.txt</t>
+          <t>django</t>
         </is>
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>1.0.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>Python package requirements.txt</t>
+          <t>A high-level Python web framework that encourages rapid development and clean, pragmatic design.</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>Unknown / Open Source Community</t>
+          <t>Django Software Foundation (DSF)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -1308,62 +1308,62 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>django, jinja2, numpy, requests, urllib3</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>GHSA-337x-4q8g-prc5, GHSA-68w8-qjq3-2gfm, GHSA-6c3j-c64m-qhgq, GHSA-6c7v-2f49-8h26, GHSA-6mx3-3vqg-hpp2, GHSA-6r97-cj55-9hrq, GHSA-6w2r-r2m5-xq5w, GHSA-7rp2-fm2h-wchj, GHSA-7xr5-9hcq-chf9, GHSA-8x94-hmjh-97hq, GHSA-c4qh-4vgv-qc6g, GHSA-frmv-pr5f-9mcr, GHSA-h5jv-4p7w-64jg, GHSA-hmr4-m2h5-33qx, GHSA-hvmf-r92r-27hr, GHSA-qw25-v68c-qjf3, GHSA-rrqc-c2jx-6jgv, GHSA-v9qg-3j8p-r63v, GHSA-vfq6-hq5r-27r6, GHSA-wh4h-v3f2-r2pp, CVE-2018-16984, CVE-2019-11358, CVE-2019-12308, CVE-2019-12781, CVE-2019-14232, CVE-2019-14233, CVE-2019-14234, CVE-2019-14235, CVE-2019-19118, CVE-2019-19844, CVE-2019-3498, CVE-2019-6975, CVE-2020-7471, CVE-2021-33203, CVE-2022-36359, CVE-2024-45231, CVE-2025-48432, CVE-2025-57833, CVE-2025-64458, CVE-2025-64459</t>
         </is>
       </c>
       <c r="J5" s="19" t="inlineStr">
         <is>
-          <t>up-to-date</t>
+          <t>patch-available</t>
         </is>
       </c>
       <c r="K5" s="19" t="inlineStr">
         <is>
-          <t>2026-06-26T09:25:49.183802Z</t>
+          <t>2018-08-01T14:11:27.382635Z</t>
         </is>
       </c>
       <c r="L5" s="19" t="inlineStr">
         <is>
-          <t>2029-06-25T09:25:49Z</t>
+          <t>2021-07-31T14:11:27Z</t>
         </is>
       </c>
       <c r="M5" s="21" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Score 15: component type='application' (+15)</t>
+          <t>Manually overridden in config to 'critical'</t>
         </is>
       </c>
       <c r="O5" s="20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Subject to internal framework deployment guidelines</t>
         </is>
       </c>
       <c r="P5" s="20" t="inlineStr">
         <is>
-          <t>SHA-256:5a1746a9ad87d418...</t>
+          <t>SHA-256:6a47faad96b2260a...</t>
         </is>
       </c>
       <c r="Q5" s="20" t="inlineStr">
         <is>
-          <t>Scanned and verified library</t>
+          <t>Primary web backend framework</t>
         </is>
       </c>
       <c r="R5" s="19" t="inlineStr">
         <is>
-          <t>Compliance &amp; Enrichment Specialist (Team Member 3)</t>
+          <t>Client-Assigned Scanning Service</t>
         </is>
       </c>
       <c r="S5" s="20" t="inlineStr">
         <is>
-          <t>2026-06-26T09:25:48Z</t>
+          <t>2026-06-29T08:32:21Z</t>
         </is>
       </c>
       <c r="T5" s="20" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="U5" s="19" t="inlineStr">
         <is>
-          <t>CycloneDX type=application</t>
+          <t>PyPI package (typically a library)</t>
         </is>
       </c>
       <c r="V5" s="19" t="inlineStr">
@@ -1383,167 +1383,20 @@
       </c>
       <c r="W5" s="20" t="inlineStr">
         <is>
-          <t>CycloneDX JSON v1.6</t>
+          <t>CycloneDX JSON v1.6 (Merged)</t>
         </is>
       </c>
       <c r="X5" s="19" t="inlineStr">
         <is>
-          <t>pkg:pypi/requirements.txt@1.0.0</t>
+          <t>pkg:pypi/django@2.1</t>
         </is>
       </c>
       <c r="Y5" s="20" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Z5" s="20" t="inlineStr">
-        <is>
-          <t>+25: Hash/checksum verified
-+20: PURL identifier available
-+15: License identified (Apache-2.0)</t>
-        </is>
-      </c>
-      <c r="AA5" s="20" t="inlineStr">
-        <is>
-          <t>PyPI</t>
-        </is>
-      </c>
-      <c r="AB5" s="20" t="inlineStr">
-        <is>
-          <t>https://pypi.org/project/requirements.txt/</t>
-        </is>
-      </c>
-      <c r="AC5" s="20" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="29" t="inlineStr">
-        <is>
-          <t>django</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>A high-level Python web framework that encourages rapid development and clean, pragmatic design.</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="inlineStr">
-        <is>
-          <t>Django Software Foundation (DSF)</t>
-        </is>
-      </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="G6" s="23" t="inlineStr">
-        <is>
-          <t>open-source</t>
-        </is>
-      </c>
-      <c r="H6" s="23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I6" s="23" t="inlineStr">
-        <is>
-          <t>CVE-2018-16984, CVE-2019-11358, CVE-2019-12308, CVE-2019-12781, CVE-2019-14232, CVE-2019-14233, CVE-2019-14234, CVE-2019-14235, CVE-2019-19118, CVE-2019-19844, CVE-2019-3498, CVE-2019-6975, CVE-2020-7471, CVE-2021-33203, CVE-2022-36359, CVE-2024-45231, CVE-2025-48432, CVE-2025-57833, CVE-2025-64458, CVE-2025-64459</t>
-        </is>
-      </c>
-      <c r="J6" s="22" t="inlineStr">
-        <is>
-          <t>patch-available</t>
-        </is>
-      </c>
-      <c r="K6" s="22" t="inlineStr">
-        <is>
-          <t>2018-08-01T14:11:27.382635Z</t>
-        </is>
-      </c>
-      <c r="L6" s="22" t="inlineStr">
-        <is>
-          <t>2021-07-31T14:11:27Z</t>
-        </is>
-      </c>
-      <c r="M6" s="24" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="N6" s="22" t="inlineStr">
-        <is>
-          <t>Manually overridden in config to 'critical'</t>
-        </is>
-      </c>
-      <c r="O6" s="23" t="inlineStr">
-        <is>
-          <t>Subject to internal framework deployment guidelines</t>
-        </is>
-      </c>
-      <c r="P6" s="23" t="inlineStr">
-        <is>
-          <t>SHA-256:6a47faad96b2260a...</t>
-        </is>
-      </c>
-      <c r="Q6" s="23" t="inlineStr">
-        <is>
-          <t>Primary web backend framework</t>
-        </is>
-      </c>
-      <c r="R6" s="22" t="inlineStr">
-        <is>
-          <t>Compliance &amp; Enrichment Specialist (Team Member 3)</t>
-        </is>
-      </c>
-      <c r="S6" s="23" t="inlineStr">
-        <is>
-          <t>2026-06-26T09:25:48Z</t>
-        </is>
-      </c>
-      <c r="T6" s="23" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="U6" s="22" t="inlineStr">
-        <is>
-          <t>PyPI package (typically a library)</t>
-        </is>
-      </c>
-      <c r="V6" s="22" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="W6" s="23" t="inlineStr">
-        <is>
-          <t>CycloneDX JSON v1.6</t>
-        </is>
-      </c>
-      <c r="X6" s="22" t="inlineStr">
-        <is>
-          <t>pkg:pypi/django@2.1</t>
-        </is>
-      </c>
-      <c r="Y6" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Z6" s="23" t="inlineStr">
         <is>
           <t>+30: Version confirmed from package registry (API available)
 +25: Hash/checksum verified
@@ -1552,295 +1405,147 @@
 +10: Manually reviewed in config overrides</t>
         </is>
       </c>
-      <c r="AA6" s="23" t="inlineStr">
+      <c r="AA5" s="20" t="inlineStr">
         <is>
           <t>PyPI</t>
         </is>
       </c>
-      <c r="AB6" s="23" t="inlineStr">
+      <c r="AB5" s="20" t="inlineStr">
         <is>
           <t>https://pypi.org/project/django/</t>
         </is>
       </c>
-      <c r="AC6" s="23" t="inlineStr">
+      <c r="AC5" s="20" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="28" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>jinja2</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>A very fast and expressive template engine.</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>Unknown / Open Source Community</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>Pallets Projects</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>open-source</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
-        <is>
-          <t>CVE-2019-10906, CVE-2020-28493, CVE-2024-22195, CVE-2024-34064, CVE-2024-56326, CVE-2025-27516</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>GHSA-462w-v97r-4m45, GHSA-cpwx-vrp4-4pq7, GHSA-g3rq-g295-4j3m, GHSA-h5c8-rqwp-cp95, GHSA-h75v-3vvj-5mfj, GHSA-q2x7-8rv6-6q7h, CVE-2019-10906, CVE-2020-28493, CVE-2024-22195, CVE-2024-34064, CVE-2024-56326, CVE-2025-27516</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>patch-available</t>
         </is>
       </c>
-      <c r="K7" s="19" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t>2017-11-08T20:13:42.279540Z</t>
         </is>
       </c>
-      <c r="L7" s="19" t="inlineStr">
+      <c r="L6" s="22" t="inlineStr">
         <is>
           <t>2020-11-07T20:13:42Z</t>
         </is>
       </c>
-      <c r="M7" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="N7" s="19" t="inlineStr">
-        <is>
-          <t>Score 10: component type='library' (+10)</t>
-        </is>
-      </c>
-      <c r="O7" s="20" t="inlineStr">
+      <c r="M6" s="24" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N6" s="22" t="inlineStr">
+        <is>
+          <t>Manually overridden in config to 'medium'</t>
+        </is>
+      </c>
+      <c r="O6" s="23" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="P7" s="20" t="inlineStr">
+      <c r="P6" s="23" t="inlineStr">
         <is>
           <t>SHA-256:bea121f34d38d518...</t>
         </is>
       </c>
-      <c r="Q7" s="20" t="inlineStr">
-        <is>
-          <t>Scanned and verified library</t>
-        </is>
-      </c>
-      <c r="R7" s="19" t="inlineStr">
-        <is>
-          <t>Compliance &amp; Enrichment Specialist (Team Member 3)</t>
-        </is>
-      </c>
-      <c r="S7" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-26T09:25:48Z</t>
-        </is>
-      </c>
-      <c r="T7" s="20" t="inlineStr">
+      <c r="Q6" s="23" t="inlineStr">
+        <is>
+          <t>Modern and designer-friendly templating language for Python</t>
+        </is>
+      </c>
+      <c r="R6" s="22" t="inlineStr">
+        <is>
+          <t>Client-Assigned Scanning Service</t>
+        </is>
+      </c>
+      <c r="S6" s="23" t="inlineStr">
+        <is>
+          <t>2026-06-29T08:32:21Z</t>
+        </is>
+      </c>
+      <c r="T6" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="U7" s="19" t="inlineStr">
+      <c r="U6" s="22" t="inlineStr">
         <is>
           <t>PyPI package (typically a library)</t>
         </is>
       </c>
-      <c r="V7" s="19" t="inlineStr">
+      <c r="V6" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="W7" s="20" t="inlineStr">
-        <is>
-          <t>CycloneDX JSON v1.6</t>
-        </is>
-      </c>
-      <c r="X7" s="19" t="inlineStr">
+      <c r="W6" s="23" t="inlineStr">
+        <is>
+          <t>CycloneDX JSON v1.6 (Merged)</t>
+        </is>
+      </c>
+      <c r="X6" s="22" t="inlineStr">
         <is>
           <t>pkg:pypi/jinja2@2.10</t>
         </is>
       </c>
-      <c r="Y7" s="20" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="Z7" s="20" t="inlineStr">
-        <is>
-          <t>+30: Version confirmed from package registry (API available)
-+25: Hash/checksum verified
-+20: PURL identifier available
-+15: License identified (Apache-2.0)</t>
-        </is>
-      </c>
-      <c r="AA7" s="20" t="inlineStr">
-        <is>
-          <t>PyPI</t>
-        </is>
-      </c>
-      <c r="AB7" s="20" t="inlineStr">
-        <is>
-          <t>https://pypi.org/project/jinja2/</t>
-        </is>
-      </c>
-      <c r="AC7" s="20" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="29" t="inlineStr">
-        <is>
-          <t>numpy</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>1.15.0</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>Fundamental package for array computing in Python</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="inlineStr">
-        <is>
-          <t>NumPy Developers</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="G8" s="23" t="inlineStr">
-        <is>
-          <t>open-source</t>
-        </is>
-      </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I8" s="23" t="inlineStr">
-        <is>
-          <t>CVE-2019-6446, CVE-2021-33430, CVE-2021-34141, CVE-2021-41495, CVE-2021-41496</t>
-        </is>
-      </c>
-      <c r="J8" s="22" t="inlineStr">
-        <is>
-          <t>patch-available</t>
-        </is>
-      </c>
-      <c r="K8" s="22" t="inlineStr">
-        <is>
-          <t>2018-07-23T16:03:25.445499Z</t>
-        </is>
-      </c>
-      <c r="L8" s="22" t="inlineStr">
-        <is>
-          <t>2021-07-22T16:03:25Z</t>
-        </is>
-      </c>
-      <c r="M8" s="25" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="N8" s="22" t="inlineStr">
-        <is>
-          <t>Manually overridden in config to 'medium'</t>
-        </is>
-      </c>
-      <c r="O8" s="23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="P8" s="23" t="inlineStr">
-        <is>
-          <t>SHA-256:a890e78aadf77316...</t>
-        </is>
-      </c>
-      <c r="Q8" s="23" t="inlineStr">
-        <is>
-          <t>Numeric and mathematical computation core package</t>
-        </is>
-      </c>
-      <c r="R8" s="22" t="inlineStr">
-        <is>
-          <t>Compliance &amp; Enrichment Specialist (Team Member 3)</t>
-        </is>
-      </c>
-      <c r="S8" s="23" t="inlineStr">
-        <is>
-          <t>2026-06-26T09:25:48Z</t>
-        </is>
-      </c>
-      <c r="T8" s="23" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="U8" s="22" t="inlineStr">
-        <is>
-          <t>PyPI package (typically a library)</t>
-        </is>
-      </c>
-      <c r="V8" s="22" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="W8" s="23" t="inlineStr">
-        <is>
-          <t>CycloneDX JSON v1.6</t>
-        </is>
-      </c>
-      <c r="X8" s="22" t="inlineStr">
-        <is>
-          <t>pkg:pypi/numpy@1.15.0</t>
-        </is>
-      </c>
-      <c r="Y8" s="23" t="inlineStr">
+      <c r="Y6" s="23" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="Z8" s="23" t="inlineStr">
+      <c r="Z6" s="23" t="inlineStr">
         <is>
           <t>+30: Version confirmed from package registry (API available)
 +25: Hash/checksum verified
@@ -1849,147 +1554,147 @@
 +10: Manually reviewed in config overrides</t>
         </is>
       </c>
-      <c r="AA8" s="23" t="inlineStr">
+      <c r="AA6" s="23" t="inlineStr">
         <is>
           <t>PyPI</t>
         </is>
       </c>
-      <c r="AB8" s="23" t="inlineStr">
-        <is>
-          <t>https://pypi.org/project/numpy/</t>
-        </is>
-      </c>
-      <c r="AC8" s="23" t="inlineStr">
+      <c r="AB6" s="23" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/jinja2/</t>
+        </is>
+      </c>
+      <c r="AC6" s="23" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="28" t="inlineStr">
-        <is>
-          <t>requests</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>2.20.0</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>Python HTTP for Humans.</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>Kenneth Reitz &amp; Requests Community</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>numpy</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>1.15.0</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>Fundamental package for array computing in Python</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>NumPy Developers</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>open-source</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>CVE-2023-32681, CVE-2024-35195, CVE-2024-47081, CVE-2026-25645</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>GHSA-5545-2q6w-2gh6, GHSA-6p56-wp2h-9hxr, GHSA-9fq2-x9r6-wfmf, GHSA-f7c7-j99h-c22f, GHSA-fpfv-jqm9-f5jm, CVE-2019-6446, CVE-2021-33430, CVE-2021-34141, CVE-2021-41495, CVE-2021-41496</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>patch-available</t>
         </is>
       </c>
-      <c r="K9" s="19" t="inlineStr">
-        <is>
-          <t>2018-10-18T15:46:10.776819Z</t>
-        </is>
-      </c>
-      <c r="L9" s="19" t="inlineStr">
-        <is>
-          <t>2021-10-17T15:46:10Z</t>
-        </is>
-      </c>
-      <c r="M9" s="26" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="N9" s="19" t="inlineStr">
-        <is>
-          <t>Manually overridden in config to 'high'</t>
-        </is>
-      </c>
-      <c r="O9" s="20" t="inlineStr">
+      <c r="K7" s="19" t="inlineStr">
+        <is>
+          <t>2018-07-23T16:03:25.445499Z</t>
+        </is>
+      </c>
+      <c r="L7" s="19" t="inlineStr">
+        <is>
+          <t>2021-07-22T16:03:25Z</t>
+        </is>
+      </c>
+      <c r="M7" s="24" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N7" s="19" t="inlineStr">
+        <is>
+          <t>Manually overridden in config to 'medium'</t>
+        </is>
+      </c>
+      <c r="O7" s="20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="P9" s="20" t="inlineStr">
-        <is>
-          <t>SHA-256:29a9bb27fe60f047...</t>
-        </is>
-      </c>
-      <c r="Q9" s="20" t="inlineStr">
-        <is>
-          <t>Critical HTTP client library used for core backend integrations</t>
-        </is>
-      </c>
-      <c r="R9" s="19" t="inlineStr">
-        <is>
-          <t>Compliance &amp; Enrichment Specialist (Team Member 3)</t>
-        </is>
-      </c>
-      <c r="S9" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-26T09:25:48Z</t>
-        </is>
-      </c>
-      <c r="T9" s="20" t="inlineStr">
+      <c r="P7" s="20" t="inlineStr">
+        <is>
+          <t>SHA-256:a890e78aadf77316...</t>
+        </is>
+      </c>
+      <c r="Q7" s="20" t="inlineStr">
+        <is>
+          <t>Numeric and mathematical computation core package</t>
+        </is>
+      </c>
+      <c r="R7" s="19" t="inlineStr">
+        <is>
+          <t>Client-Assigned Scanning Service</t>
+        </is>
+      </c>
+      <c r="S7" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-29T08:32:21Z</t>
+        </is>
+      </c>
+      <c r="T7" s="20" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="U9" s="19" t="inlineStr">
+      <c r="U7" s="19" t="inlineStr">
         <is>
           <t>PyPI package (typically a library)</t>
         </is>
       </c>
-      <c r="V9" s="19" t="inlineStr">
+      <c r="V7" s="19" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="W9" s="20" t="inlineStr">
-        <is>
-          <t>CycloneDX JSON v1.6</t>
-        </is>
-      </c>
-      <c r="X9" s="19" t="inlineStr">
-        <is>
-          <t>pkg:pypi/requests@2.20.0</t>
-        </is>
-      </c>
-      <c r="Y9" s="20" t="inlineStr">
+      <c r="W7" s="20" t="inlineStr">
+        <is>
+          <t>CycloneDX JSON v1.6 (Merged)</t>
+        </is>
+      </c>
+      <c r="X7" s="19" t="inlineStr">
+        <is>
+          <t>pkg:pypi/numpy@1.15.0</t>
+        </is>
+      </c>
+      <c r="Y7" s="20" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="Z9" s="20" t="inlineStr">
+      <c r="Z7" s="20" t="inlineStr">
         <is>
           <t>+30: Version confirmed from package registry (API available)
 +25: Hash/checksum verified
@@ -1998,147 +1703,147 @@
 +10: Manually reviewed in config overrides</t>
         </is>
       </c>
-      <c r="AA9" s="20" t="inlineStr">
+      <c r="AA7" s="20" t="inlineStr">
         <is>
           <t>PyPI</t>
         </is>
       </c>
-      <c r="AB9" s="20" t="inlineStr">
-        <is>
-          <t>https://pypi.org/project/requests/</t>
-        </is>
-      </c>
-      <c r="AC9" s="20" t="inlineStr">
+      <c r="AB7" s="20" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/numpy/</t>
+        </is>
+      </c>
+      <c r="AC7" s="20" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="29" t="inlineStr">
-        <is>
-          <t>urllib3</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>1.24.2</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>HTTP library with thread-safe connection pooling, file post, and more.</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>urllib3 Contributors</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>requests</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>2.20.0</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Python HTTP for Humans.</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>Kenneth Reitz &amp; Requests Community</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>open-source</t>
         </is>
       </c>
-      <c r="H10" s="23" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>CVE-2019-11236, CVE-2020-26137, CVE-2023-43804, CVE-2023-45803, CVE-2024-37891, CVE-2025-50181, CVE-2025-66418, CVE-2025-66471, CVE-2026-21441, CVE-2026-44431</t>
-        </is>
-      </c>
-      <c r="J10" s="22" t="inlineStr">
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>GHSA-9hjg-9r4m-mvj7, GHSA-9wx4-h78v-vm56, GHSA-j8r2-6x86-q33q, CVE-2023-32681, CVE-2024-35195, CVE-2024-47081, CVE-2026-25645</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>patch-available</t>
         </is>
       </c>
-      <c r="K10" s="22" t="inlineStr">
-        <is>
-          <t>2019-04-17T17:49:45.870917Z</t>
-        </is>
-      </c>
-      <c r="L10" s="22" t="inlineStr">
-        <is>
-          <t>2022-04-16T17:49:45Z</t>
-        </is>
-      </c>
-      <c r="M10" s="26" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>2018-10-18T15:46:10.776819Z</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>2021-10-17T15:46:10Z</t>
+        </is>
+      </c>
+      <c r="M8" s="25" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="N10" s="22" t="inlineStr">
+      <c r="N8" s="22" t="inlineStr">
         <is>
           <t>Manually overridden in config to 'high'</t>
         </is>
       </c>
-      <c r="O10" s="23" t="inlineStr">
+      <c r="O8" s="23" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="P10" s="23" t="inlineStr">
-        <is>
-          <t>SHA-256:889a9b94b6891674...</t>
-        </is>
-      </c>
-      <c r="Q10" s="23" t="inlineStr">
-        <is>
-          <t>Core networking transport library for HTTP calls</t>
-        </is>
-      </c>
-      <c r="R10" s="22" t="inlineStr">
-        <is>
-          <t>Compliance &amp; Enrichment Specialist (Team Member 3)</t>
-        </is>
-      </c>
-      <c r="S10" s="23" t="inlineStr">
-        <is>
-          <t>2026-06-26T09:25:48Z</t>
-        </is>
-      </c>
-      <c r="T10" s="23" t="inlineStr">
+      <c r="P8" s="23" t="inlineStr">
+        <is>
+          <t>SHA-256:29a9bb27fe60f047...</t>
+        </is>
+      </c>
+      <c r="Q8" s="23" t="inlineStr">
+        <is>
+          <t>Critical HTTP client library used for core backend integrations</t>
+        </is>
+      </c>
+      <c r="R8" s="22" t="inlineStr">
+        <is>
+          <t>Client-Assigned Scanning Service</t>
+        </is>
+      </c>
+      <c r="S8" s="23" t="inlineStr">
+        <is>
+          <t>2026-06-29T08:32:21Z</t>
+        </is>
+      </c>
+      <c r="T8" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="U10" s="22" t="inlineStr">
+      <c r="U8" s="22" t="inlineStr">
         <is>
           <t>PyPI package (typically a library)</t>
         </is>
       </c>
-      <c r="V10" s="22" t="inlineStr">
+      <c r="V8" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="W10" s="23" t="inlineStr">
-        <is>
-          <t>CycloneDX JSON v1.6</t>
-        </is>
-      </c>
-      <c r="X10" s="22" t="inlineStr">
-        <is>
-          <t>pkg:pypi/urllib3@1.24.2</t>
-        </is>
-      </c>
-      <c r="Y10" s="23" t="inlineStr">
+      <c r="W8" s="23" t="inlineStr">
+        <is>
+          <t>CycloneDX JSON v1.6 (Merged)</t>
+        </is>
+      </c>
+      <c r="X8" s="22" t="inlineStr">
+        <is>
+          <t>pkg:pypi/requests@2.20.0</t>
+        </is>
+      </c>
+      <c r="Y8" s="23" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="Z10" s="23" t="inlineStr">
+      <c r="Z8" s="23" t="inlineStr">
         <is>
           <t>+30: Version confirmed from package registry (API available)
 +25: Hash/checksum verified
@@ -2147,6 +1852,302 @@
 +10: Manually reviewed in config overrides</t>
         </is>
       </c>
+      <c r="AA8" s="23" t="inlineStr">
+        <is>
+          <t>PyPI</t>
+        </is>
+      </c>
+      <c r="AB8" s="23" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/requests/</t>
+        </is>
+      </c>
+      <c r="AC8" s="23" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>urllib3</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>1.24.2</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>HTTP library with thread-safe connection pooling, file post, and more.</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>urllib3 Contributors</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>open-source</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>GHSA-2xpw-w6gg-jr37, GHSA-34jh-p97f-mpxf, GHSA-38jv-5279-wg99, GHSA-g4mx-q9vg-27p4, GHSA-gm62-xv2j-4w53, GHSA-pq67-6m6q-mj2v, GHSA-r64q-w8jr-g9qp, GHSA-v845-jxx5-vc9f, GHSA-wqvq-5m8c-6g24, CVE-2019-11236, CVE-2020-26137, CVE-2023-43804, CVE-2023-45803, CVE-2024-37891, CVE-2025-50181, CVE-2025-66418, CVE-2025-66471, CVE-2026-21441, CVE-2026-44431</t>
+        </is>
+      </c>
+      <c r="J9" s="19" t="inlineStr">
+        <is>
+          <t>patch-available</t>
+        </is>
+      </c>
+      <c r="K9" s="19" t="inlineStr">
+        <is>
+          <t>2019-04-17T17:49:45.870917Z</t>
+        </is>
+      </c>
+      <c r="L9" s="19" t="inlineStr">
+        <is>
+          <t>2022-04-16T17:49:45Z</t>
+        </is>
+      </c>
+      <c r="M9" s="25" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="N9" s="19" t="inlineStr">
+        <is>
+          <t>Manually overridden in config to 'high'</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P9" s="20" t="inlineStr">
+        <is>
+          <t>SHA-256:889a9b94b6891674...</t>
+        </is>
+      </c>
+      <c r="Q9" s="20" t="inlineStr">
+        <is>
+          <t>Core networking transport library for HTTP calls</t>
+        </is>
+      </c>
+      <c r="R9" s="19" t="inlineStr">
+        <is>
+          <t>Client-Assigned Scanning Service</t>
+        </is>
+      </c>
+      <c r="S9" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-29T08:32:21Z</t>
+        </is>
+      </c>
+      <c r="T9" s="20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U9" s="19" t="inlineStr">
+        <is>
+          <t>PyPI package (typically a library)</t>
+        </is>
+      </c>
+      <c r="V9" s="19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="W9" s="20" t="inlineStr">
+        <is>
+          <t>CycloneDX JSON v1.6 (Merged)</t>
+        </is>
+      </c>
+      <c r="X9" s="19" t="inlineStr">
+        <is>
+          <t>pkg:pypi/urllib3@1.24.2</t>
+        </is>
+      </c>
+      <c r="Y9" s="20" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z9" s="20" t="inlineStr">
+        <is>
+          <t>+30: Version confirmed from package registry (API available)
++25: Hash/checksum verified
++20: PURL identifier available
++15: License identified (Apache-2.0)
++10: Manually reviewed in config overrides</t>
+        </is>
+      </c>
+      <c r="AA9" s="20" t="inlineStr">
+        <is>
+          <t>PyPI</t>
+        </is>
+      </c>
+      <c r="AB9" s="20" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/urllib3/</t>
+        </is>
+      </c>
+      <c r="AC9" s="20" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>requirements.txt</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Python package requirements.txt</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>Unknown / Open Source Community</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>open-source</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>jinja2, urllib3, requests, numpy, django</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>up-to-date</t>
+        </is>
+      </c>
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-29T08:32:22.033242Z</t>
+        </is>
+      </c>
+      <c r="L10" s="22" t="inlineStr">
+        <is>
+          <t>2029-06-28T08:32:22Z</t>
+        </is>
+      </c>
+      <c r="M10" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N10" s="22" t="inlineStr">
+        <is>
+          <t>Score 15: component type='application' (+15)</t>
+        </is>
+      </c>
+      <c r="O10" s="23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P10" s="23" t="inlineStr">
+        <is>
+          <t>SHA-256:5a1746a9ad87d418...</t>
+        </is>
+      </c>
+      <c r="Q10" s="23" t="inlineStr">
+        <is>
+          <t>Merged and reconciled from Syft &amp; Trivy SBOM feeds</t>
+        </is>
+      </c>
+      <c r="R10" s="22" t="inlineStr">
+        <is>
+          <t>Client-Assigned Scanning Service</t>
+        </is>
+      </c>
+      <c r="S10" s="23" t="inlineStr">
+        <is>
+          <t>2026-06-29T08:32:21Z</t>
+        </is>
+      </c>
+      <c r="T10" s="23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U10" s="22" t="inlineStr">
+        <is>
+          <t>CycloneDX type=application</t>
+        </is>
+      </c>
+      <c r="V10" s="22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="W10" s="23" t="inlineStr">
+        <is>
+          <t>CycloneDX JSON v1.6 (Merged)</t>
+        </is>
+      </c>
+      <c r="X10" s="22" t="inlineStr">
+        <is>
+          <t>pkg:pypi/requirements.txt@1.0.0</t>
+        </is>
+      </c>
+      <c r="Y10" s="23" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Z10" s="23" t="inlineStr">
+        <is>
+          <t>+25: Hash/checksum verified
++20: PURL identifier available
++15: License identified (Apache-2.0)</t>
+        </is>
+      </c>
       <c r="AA10" s="23" t="inlineStr">
         <is>
           <t>PyPI</t>
@@ -2154,7 +2155,7 @@
       </c>
       <c r="AB10" s="23" t="inlineStr">
         <is>
-          <t>https://pypi.org/project/urllib3/</t>
+          <t>https://pypi.org/project/requirements.txt/</t>
         </is>
       </c>
       <c r="AC10" s="23" t="inlineStr">
@@ -2179,13 +2180,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -2248,27 +2249,27 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>CVE-2018-16984</t>
+          <t>GHSA-2xpw-w6gg-jr37</t>
         </is>
       </c>
       <c r="C4" s="30" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E4" s="20" t="inlineStr">
         <is>
-          <t>An issue was discovered in Django 2.1 before 2.1.2, in which unprivileged users can read the password hashes of arbitrar</t>
+          <t>urllib3 streaming API improperly handles highly compressed data</t>
         </is>
       </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
-          <t>django</t>
+          <t>urllib3</t>
         </is>
       </c>
       <c r="G4" s="19" t="inlineStr">
@@ -2278,7 +2279,7 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-2xpw-w6gg-jr37</t>
         </is>
       </c>
     </row>
@@ -2288,27 +2289,27 @@
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>CVE-2019-10906</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
+          <t>GHSA-337x-4q8g-prc5</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
-          <t>In Pallets Jinja before 2.10.1, str.format_map allows a sandbox escape.</t>
+          <t>Improper Input Validation in Django</t>
         </is>
       </c>
       <c r="F5" s="23" t="inlineStr">
         <is>
-          <t>jinja2</t>
+          <t>django</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -2318,7 +2319,7 @@
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-337x-4q8g-prc5</t>
         </is>
       </c>
     </row>
@@ -2328,22 +2329,22 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>CVE-2019-11236</t>
-        </is>
-      </c>
-      <c r="C6" s="30" t="inlineStr">
+          <t>GHSA-34jh-p97f-mpxf</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>In the urllib3 library through 1.24.1 for Python, CRLF injection is possible if the attacker controls the request parame</t>
+          <t>urllib3's Proxy-Authorization request header isn't stripped during cross-origin redirects</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -2358,7 +2359,7 @@
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-34jh-p97f-mpxf</t>
         </is>
       </c>
     </row>
@@ -2368,27 +2369,27 @@
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>CVE-2019-11358</t>
+          <t>GHSA-38jv-5279-wg99</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>jQuery before 3.4.0, as used in Drupal, Backdrop CMS, and other products, mishandles jQuery.extend(true, {}, ...) becaus</t>
+          <t>Decompression-bomb safeguards bypassed when following HTTP redirects (streaming API)</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>django</t>
+          <t>urllib3</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -2398,7 +2399,7 @@
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-38jv-5279-wg99</t>
         </is>
       </c>
     </row>
@@ -2408,27 +2409,27 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>CVE-2019-12308</t>
+          <t>GHSA-462w-v97r-4m45</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>An issue was discovered in Django 1.11 before 1.11.21, 2.1 before 2.1.9, and 2.2 before 2.2.2. The clickable Current URL</t>
+          <t>Jinja2 sandbox escape via string formatting</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>django</t>
+          <t>jinja2</t>
         </is>
       </c>
       <c r="G8" s="19" t="inlineStr">
@@ -2438,7 +2439,7 @@
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-462w-v97r-4m45</t>
         </is>
       </c>
     </row>
@@ -2448,27 +2449,27 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>CVE-2019-12781</t>
+          <t>GHSA-5545-2q6w-2gh6</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>An issue was discovered in Django 1.11 before 1.11.22, 2.1 before 2.1.10, and 2.2 before 2.2.3. An HTTP request is not r</t>
+          <t>NumPy NULL Pointer Dereference</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>django</t>
+          <t>numpy</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -2478,7 +2479,7 @@
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-5545-2q6w-2gh6</t>
         </is>
       </c>
     </row>
@@ -2488,22 +2489,22 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>CVE-2019-14232</t>
+          <t>GHSA-68w8-qjq3-2gfm</t>
         </is>
       </c>
       <c r="C10" s="31" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>An issue was discovered in Django 1.11.x before 1.11.23, 2.1.x before 2.1.11, and 2.2.x before 2.2.4. If django.utils.te</t>
+          <t>Path Traversal in Django</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -2518,7 +2519,7 @@
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-68w8-qjq3-2gfm</t>
         </is>
       </c>
     </row>
@@ -2528,22 +2529,22 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>CVE-2019-14233</t>
+          <t>GHSA-6c3j-c64m-qhgq</t>
         </is>
       </c>
       <c r="C11" s="31" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>An issue was discovered in Django 1.11.x before 1.11.23, 2.1.x before 2.1.11, and 2.2.x before 2.2.4. Due to the behavio</t>
+          <t>XSS in jQuery as used in Drupal, Backdrop CMS, and other products</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
@@ -2558,7 +2559,7 @@
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-6c3j-c64m-qhgq</t>
         </is>
       </c>
     </row>
@@ -2568,22 +2569,22 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>CVE-2019-14234</t>
-        </is>
-      </c>
-      <c r="C12" s="32" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
+          <t>GHSA-6c7v-2f49-8h26</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>An issue was discovered in Django 1.11.x before 1.11.23, 2.1.x before 2.1.11, and 2.2.x before 2.2.4. Due to an error in</t>
+          <t>Django Incorrect HTTP detection with reverse-proxy connecting via HTTPS</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -2598,7 +2599,7 @@
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-6c7v-2f49-8h26</t>
         </is>
       </c>
     </row>
@@ -2608,22 +2609,22 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>CVE-2019-14235</t>
+          <t>GHSA-6mx3-3vqg-hpp2</t>
         </is>
       </c>
       <c r="C13" s="31" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">An issue was discovered in Django 1.11.x before 1.11.23, 2.1.x before 2.1.11, and 2.2.x before 2.2.4. If passed certain </t>
+          <t>Django allows unprivileged users to read the password hashes of arbitrary accounts</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -2638,7 +2639,7 @@
       </c>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-6mx3-3vqg-hpp2</t>
         </is>
       </c>
     </row>
@@ -2648,27 +2649,27 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>CVE-2019-19118</t>
+          <t>GHSA-6p56-wp2h-9hxr</t>
         </is>
       </c>
       <c r="C14" s="31" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Django 2.1 before 2.1.15 and 2.2 before 2.2.8 allows unintended model editing. A Django model admin displaying inline re</t>
+          <t>NumPy Buffer Overflow (Disputed)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>django</t>
+          <t>numpy</t>
         </is>
       </c>
       <c r="G14" s="19" t="inlineStr">
@@ -2678,7 +2679,7 @@
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-6p56-wp2h-9hxr</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2689,7 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>CVE-2019-19844</t>
+          <t>GHSA-6r97-cj55-9hrq</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -2698,12 +2699,12 @@
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Django before 1.11.27, 2.x before 2.2.9, and 3.x before 3.0.1 allows account takeover. A suitably crafted email address </t>
+          <t>SQL Injection in Django</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
@@ -2718,7 +2719,7 @@
       </c>
       <c r="H15" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-6r97-cj55-9hrq</t>
         </is>
       </c>
     </row>
@@ -2728,22 +2729,22 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>CVE-2019-3498</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="inlineStr">
+          <t>GHSA-6w2r-r2m5-xq5w</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>In Django 1.11.x before 1.11.18, 2.0.x before 2.0.10, and 2.1.x before 2.1.5, an Improper Neutralization of Special Elem</t>
+          <t>Django is subject to SQL injection through its column aliases</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -2758,7 +2759,7 @@
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-6w2r-r2m5-xq5w</t>
         </is>
       </c>
     </row>
@@ -2768,27 +2769,27 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>CVE-2019-6446</t>
-        </is>
-      </c>
-      <c r="C17" s="30" t="inlineStr">
+          <t>GHSA-7rp2-fm2h-wchj</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
-          <t>An issue was discovered in NumPy before 1.16.3. It uses the pickle Python module unsafely, which allows remote attackers</t>
+          <t>Django Cross-site Scripting in AdminURLFieldWidget</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>numpy</t>
+          <t>django</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -2798,7 +2799,7 @@
       </c>
       <c r="H17" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-7rp2-fm2h-wchj</t>
         </is>
       </c>
     </row>
@@ -2808,22 +2809,22 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>CVE-2019-6975</t>
+          <t>GHSA-7xr5-9hcq-chf9</t>
         </is>
       </c>
       <c r="C18" s="31" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Django 1.11.x before 1.11.19, 2.0.x before 2.0.11, and 2.1.x before 2.1.6 allows Uncontrolled Memory Consumption via a m</t>
+          <t>Django Improper Output Neutralization for Logs vulnerability</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -2838,7 +2839,7 @@
       </c>
       <c r="H18" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-7xr5-9hcq-chf9</t>
         </is>
       </c>
     </row>
@@ -2848,27 +2849,27 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>CVE-2020-26137</t>
+          <t>GHSA-8x94-hmjh-97hq</t>
         </is>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>urllib3 before 1.25.9 allows CRLF injection if the attacker controls the HTTP request method, as demonstrated by inserti</t>
+          <t>Django vulnerable to Reflected File Download attack</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>urllib3</t>
+          <t>django</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -2878,7 +2879,7 @@
       </c>
       <c r="H19" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-8x94-hmjh-97hq</t>
         </is>
       </c>
     </row>
@@ -2888,27 +2889,27 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>CVE-2020-28493</t>
-        </is>
-      </c>
-      <c r="C20" s="30" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>GHSA-9fq2-x9r6-wfmf</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>This affects the package jinja2 from 0.0.0 and before 2.11.3. The ReDoS vulnerability is mainly due to the `_punctuation</t>
+          <t>Numpy Deserialization of Untrusted Data</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>jinja2</t>
+          <t>numpy</t>
         </is>
       </c>
       <c r="G20" s="19" t="inlineStr">
@@ -2918,7 +2919,7 @@
       </c>
       <c r="H20" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-9fq2-x9r6-wfmf</t>
         </is>
       </c>
     </row>
@@ -2928,27 +2929,27 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>CVE-2020-7471</t>
-        </is>
-      </c>
-      <c r="C21" s="32" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
+          <t>GHSA-9hjg-9r4m-mvj7</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Django 1.11 before 1.11.28, 2.2 before 2.2.10, and 3.0 before 3.0.3 allows SQL Injection if untrusted data is used as a </t>
+          <t>Requests vulnerable to .netrc credentials leak via malicious URLs</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>django</t>
+          <t>requests</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -2958,7 +2959,7 @@
       </c>
       <c r="H21" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-9hjg-9r4m-mvj7</t>
         </is>
       </c>
     </row>
@@ -2968,27 +2969,27 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>CVE-2021-33203</t>
-        </is>
-      </c>
-      <c r="C22" s="30" t="inlineStr">
+          <t>GHSA-9wx4-h78v-vm56</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Django before 2.2.24, 3.x before 3.1.12, and 3.2.x before 3.2.4 has a potential directory traversal via django.contrib.a</t>
+          <t>Requests `Session` object does not verify requests after making first request with verify=False</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>django</t>
+          <t>requests</t>
         </is>
       </c>
       <c r="G22" s="19" t="inlineStr">
@@ -2998,7 +2999,7 @@
       </c>
       <c r="H22" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-9wx4-h78v-vm56</t>
         </is>
       </c>
     </row>
@@ -3008,27 +3009,27 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>CVE-2021-33430</t>
+          <t>GHSA-c4qh-4vgv-qc6g</t>
         </is>
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
         <is>
-          <t>A Buffer Overflow vulnerability exists in NumPy 1.9.x in the PyArray_NewFromDescr_int function of ctors.c when specifyin</t>
+          <t>Django Denial-of-service in django.utils.text.Truncator</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t>numpy</t>
+          <t>django</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -3038,7 +3039,7 @@
       </c>
       <c r="H23" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-c4qh-4vgv-qc6g</t>
         </is>
       </c>
     </row>
@@ -3048,27 +3049,27 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>CVE-2021-34141</t>
-        </is>
-      </c>
-      <c r="C24" s="30" t="inlineStr">
+          <t>GHSA-cpwx-vrp4-4pq7</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">An incomplete string comparison in the numpy.core component in NumPy before 1.22.0 allows attackers to trigger slightly </t>
+          <t>Jinja2 vulnerable to sandbox breakout through attr filter selecting format method</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>numpy</t>
+          <t>jinja2</t>
         </is>
       </c>
       <c r="G24" s="19" t="inlineStr">
@@ -3078,7 +3079,7 @@
       </c>
       <c r="H24" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-cpwx-vrp4-4pq7</t>
         </is>
       </c>
     </row>
@@ -3088,22 +3089,22 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>CVE-2021-41495</t>
-        </is>
-      </c>
-      <c r="C25" s="30" t="inlineStr">
+          <t>GHSA-f7c7-j99h-c22f</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>Null Pointer Dereference vulnerability exists in numpy.sort in NumPy &amp;lt and 1.19 in the PyArray_DescrNew function due t</t>
+          <t>Buffer Copy without Checking Size of Input in NumPy</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -3118,7 +3119,7 @@
       </c>
       <c r="H25" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-f7c7-j99h-c22f</t>
         </is>
       </c>
     </row>
@@ -3128,22 +3129,22 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>CVE-2021-41496</t>
-        </is>
-      </c>
-      <c r="C26" s="30" t="inlineStr">
+          <t>GHSA-fpfv-jqm9-f5jm</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Buffer overflow in the array_from_pyobj function of fortranobject.c in NumPy &lt; 1.19, which allows attackers to conduct a</t>
+          <t>Incorrect Comparison in NumPy</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -3158,7 +3159,7 @@
       </c>
       <c r="H26" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-fpfv-jqm9-f5jm</t>
         </is>
       </c>
     </row>
@@ -3168,22 +3169,22 @@
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>CVE-2022-36359</t>
-        </is>
-      </c>
-      <c r="C27" s="31" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>GHSA-frmv-pr5f-9mcr</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">An issue was discovered in the HTTP FileResponse class in Django 3.2 before 3.2.15 and 4.0 before 4.0.7. An application </t>
+          <t>Django vulnerable to SQL injection via _connector keyword argument in QuerySet and Q objects.</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
@@ -3198,7 +3199,7 @@
       </c>
       <c r="H27" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-frmv-pr5f-9mcr</t>
         </is>
       </c>
     </row>
@@ -3208,27 +3209,27 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>CVE-2023-32681</t>
-        </is>
-      </c>
-      <c r="C28" s="30" t="inlineStr">
+          <t>GHSA-g3rq-g295-4j3m</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Requests is a HTTP library. Since Requests 2.3.0, Requests has been leaking Proxy-Authorization headers to destination s</t>
+          <t>Regular Expression Denial of Service (ReDoS) in Jinja2</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>requests</t>
+          <t>jinja2</t>
         </is>
       </c>
       <c r="G28" s="19" t="inlineStr">
@@ -3238,7 +3239,7 @@
       </c>
       <c r="H28" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-g3rq-g295-4j3m</t>
         </is>
       </c>
     </row>
@@ -3248,22 +3249,22 @@
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>CVE-2023-43804</t>
-        </is>
-      </c>
-      <c r="C29" s="30" t="inlineStr">
+          <t>GHSA-g4mx-q9vg-27p4</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>urllib3 is a user-friendly HTTP client library for Python. urllib3 doesn't treat the `Cookie` HTTP header special or pro</t>
+          <t>urllib3's request body not stripped after redirect from 303 status changes request method to GET</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
@@ -3278,7 +3279,7 @@
       </c>
       <c r="H29" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-g4mx-q9vg-27p4</t>
         </is>
       </c>
     </row>
@@ -3288,22 +3289,22 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>CVE-2023-45803</t>
+          <t>GHSA-gm62-xv2j-4w53</t>
         </is>
       </c>
       <c r="C30" s="30" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>urllib3 is a user-friendly HTTP client library for Python. urllib3 previously wouldn't remove the HTTP request body when</t>
+          <t>urllib3 allows an unbounded number of links in the decompression chain</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -3318,7 +3319,7 @@
       </c>
       <c r="H30" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-gm62-xv2j-4w53</t>
         </is>
       </c>
     </row>
@@ -3328,22 +3329,22 @@
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>CVE-2024-22195</t>
-        </is>
-      </c>
-      <c r="C31" s="30" t="inlineStr">
+          <t>GHSA-h5c8-rqwp-cp95</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>Jinja is an extensible templating engine. Special placeholders in the template allow writing code similar to Python synt</t>
+          <t>Jinja vulnerable to HTML attribute injection when passing user input as keys to xmlattr filter</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
@@ -3358,7 +3359,7 @@
       </c>
       <c r="H31" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-h5c8-rqwp-cp95</t>
         </is>
       </c>
     </row>
@@ -3368,27 +3369,27 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>CVE-2024-34064</t>
+          <t>GHSA-h5jv-4p7w-64jg</t>
         </is>
       </c>
       <c r="C32" s="30" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Jinja is an extensible templating engine. The `xmlattr` filter in affected versions of Jinja accepts keys containing non</t>
+          <t>Django Denial-of-service in strip_tags()</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>jinja2</t>
+          <t>django</t>
         </is>
       </c>
       <c r="G32" s="19" t="inlineStr">
@@ -3398,7 +3399,7 @@
       </c>
       <c r="H32" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-h5jv-4p7w-64jg</t>
         </is>
       </c>
     </row>
@@ -3408,27 +3409,27 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>CVE-2024-35195</t>
-        </is>
-      </c>
-      <c r="C33" s="30" t="inlineStr">
+          <t>GHSA-h75v-3vvj-5mfj</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Requests is a HTTP library. Prior to 2.32.0, when making requests through a Requests `Session`, if the first request is </t>
+          <t>Jinja vulnerable to HTML attribute injection when passing user input as keys to xmlattr filter</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t>requests</t>
+          <t>jinja2</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
@@ -3438,7 +3439,7 @@
       </c>
       <c r="H33" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-h75v-3vvj-5mfj</t>
         </is>
       </c>
     </row>
@@ -3448,27 +3449,27 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>CVE-2024-37891</t>
-        </is>
-      </c>
-      <c r="C34" s="30" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>GHSA-hmr4-m2h5-33qx</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> urllib3 is a user-friendly HTTP client library for Python. When using urllib3's proxy support with `ProxyManager`, the </t>
+          <t>SQL injection in Django</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
-          <t>urllib3</t>
+          <t>django</t>
         </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
@@ -3478,7 +3479,7 @@
       </c>
       <c r="H34" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-hmr4-m2h5-33qx</t>
         </is>
       </c>
     </row>
@@ -3488,22 +3489,22 @@
       </c>
       <c r="B35" s="23" t="inlineStr">
         <is>
-          <t>CVE-2024-45231</t>
+          <t>GHSA-hvmf-r92r-27hr</t>
         </is>
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>An issue was discovered in Django v5.1.1, v5.0.9, and v4.2.16. The django.contrib.auth.forms.PasswordResetForm class, wh</t>
+          <t>Django allows unintended model editing</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
@@ -3518,7 +3519,7 @@
       </c>
       <c r="H35" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-hvmf-r92r-27hr</t>
         </is>
       </c>
     </row>
@@ -3528,22 +3529,22 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>CVE-2024-47081</t>
-        </is>
-      </c>
-      <c r="C36" s="30" t="inlineStr">
+          <t>GHSA-j8r2-6x86-q33q</t>
+        </is>
+      </c>
+      <c r="C36" s="31" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>Requests is a HTTP library. Due to a URL parsing issue, Requests releases prior to 2.32.4 may leak .netrc credentials to</t>
+          <t>Unintended leak of Proxy-Authorization header in requests</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -3558,7 +3559,7 @@
       </c>
       <c r="H36" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-j8r2-6x86-q33q</t>
         </is>
       </c>
     </row>
@@ -3568,27 +3569,27 @@
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>CVE-2024-56326</t>
+          <t>GHSA-pq67-6m6q-mj2v</t>
         </is>
       </c>
       <c r="C37" s="31" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
         <is>
-          <t>Jinja is an extensible templating engine. Prior to 3.1.5, An oversight in how the Jinja sandboxed environment detects ca</t>
+          <t>urllib3 redirects are not disabled when retries are disabled on PoolManager instantiation</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t>jinja2</t>
+          <t>urllib3</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -3598,7 +3599,7 @@
       </c>
       <c r="H37" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-pq67-6m6q-mj2v</t>
         </is>
       </c>
     </row>
@@ -3608,22 +3609,22 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>CVE-2025-27516</t>
+          <t>GHSA-q2x7-8rv6-6q7h</t>
         </is>
       </c>
       <c r="C38" s="31" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jinja is an extensible templating engine. Prior to 3.1.6, an oversight in how the Jinja sandboxed environment interacts </t>
+          <t>Jinja has a sandbox breakout through indirect reference to format method</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
@@ -3638,7 +3639,7 @@
       </c>
       <c r="H38" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-q2x7-8rv6-6q7h</t>
         </is>
       </c>
     </row>
@@ -3648,22 +3649,22 @@
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>CVE-2025-48432</t>
+          <t>GHSA-qw25-v68c-qjf3</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E39" s="23" t="inlineStr">
         <is>
-          <t>An issue was discovered in Django 5.2 before 5.2.3, 5.1 before 5.1.11, and 4.2 before 4.2.23. Internal HTTP response log</t>
+          <t>Django has a denial-of-service vulnerability in HttpResponseRedirect and HttpResponsePermanentRedirect on Windows</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
@@ -3678,7 +3679,7 @@
       </c>
       <c r="H39" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-qw25-v68c-qjf3</t>
         </is>
       </c>
     </row>
@@ -3688,22 +3689,22 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>CVE-2025-50181</t>
-        </is>
-      </c>
-      <c r="C40" s="30" t="inlineStr">
+          <t>GHSA-r64q-w8jr-g9qp</t>
+        </is>
+      </c>
+      <c r="C40" s="31" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>urllib3 is a user-friendly HTTP client library for Python. Prior to 2.5.0, it is possible to disable redirects for all r</t>
+          <t>Improper Neutralization of CRLF Sequences in urllib3 library for Python</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
@@ -3718,7 +3719,7 @@
       </c>
       <c r="H40" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-r64q-w8jr-g9qp</t>
         </is>
       </c>
     </row>
@@ -3728,22 +3729,22 @@
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>CVE-2025-57833</t>
+          <t>GHSA-rrqc-c2jx-6jgv</t>
         </is>
       </c>
       <c r="C41" s="31" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>An issue was discovered in Django 4.2 before 4.2.24, 5.1 before 5.1.12, and 5.2 before 5.2.6. FilteredRelation is subjec</t>
+          <t>Django allows enumeration of user e-mail addresses</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
@@ -3758,7 +3759,7 @@
       </c>
       <c r="H41" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-rrqc-c2jx-6jgv</t>
         </is>
       </c>
     </row>
@@ -3768,28 +3769,27 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>CVE-2025-64458</t>
-        </is>
-      </c>
-      <c r="C42" s="31" t="inlineStr">
+          <t>GHSA-v845-jxx5-vc9f</t>
+        </is>
+      </c>
+      <c r="C42" s="30" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>An issue was discovered in 5.1 before 5.1.14, 4.2 before 4.2.26, and 5.2 before 5.2.8.
-NFKC normalization in Python is s</t>
+          <t>`Cookie` HTTP header isn't stripped on cross-origin redirects</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
         <is>
-          <t>django</t>
+          <t>urllib3</t>
         </is>
       </c>
       <c r="G42" s="19" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="H42" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-v845-jxx5-vc9f</t>
         </is>
       </c>
     </row>
@@ -3809,23 +3809,22 @@
       </c>
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>CVE-2025-64459</t>
-        </is>
-      </c>
-      <c r="C43" s="32" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
+          <t>GHSA-v9qg-3j8p-r63v</t>
+        </is>
+      </c>
+      <c r="C43" s="30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D43" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">An issue was discovered in 5.1 before 5.1.14, 4.2 before 4.2.26, and 5.2 before 5.2.8.
-The methods `QuerySet.filter()`, </t>
+          <t>Uncontrolled Recursion in Django</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
@@ -3840,7 +3839,7 @@
       </c>
       <c r="H43" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-v9qg-3j8p-r63v</t>
         </is>
       </c>
     </row>
@@ -3850,27 +3849,27 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>CVE-2025-66418</t>
-        </is>
-      </c>
-      <c r="C44" s="31" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>GHSA-vfq6-hq5r-27r6</t>
+        </is>
+      </c>
+      <c r="C44" s="32" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>urllib3 is a user-friendly HTTP client library for Python. Starting in version 1.24 and prior to 2.6.0, the number of li</t>
+          <t>Django Potential account hijack via password reset form</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
         <is>
-          <t>urllib3</t>
+          <t>django</t>
         </is>
       </c>
       <c r="G44" s="19" t="inlineStr">
@@ -3880,7 +3879,7 @@
       </c>
       <c r="H44" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-vfq6-hq5r-27r6</t>
         </is>
       </c>
     </row>
@@ -3890,27 +3889,27 @@
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>CVE-2025-66471</t>
-        </is>
-      </c>
-      <c r="C45" s="31" t="inlineStr">
+          <t>GHSA-wh4h-v3f2-r2pp</t>
+        </is>
+      </c>
+      <c r="C45" s="30" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
         <is>
-          <t>urllib3 is a user-friendly HTTP client library for Python. Starting in version 1.0 and prior to 2.6.0, the Streaming API</t>
+          <t>Uncontrolled Memory Consumption in Django</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t>urllib3</t>
+          <t>django</t>
         </is>
       </c>
       <c r="G45" s="22" t="inlineStr">
@@ -3920,7 +3919,7 @@
       </c>
       <c r="H45" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-wh4h-v3f2-r2pp</t>
         </is>
       </c>
     </row>
@@ -3930,22 +3929,22 @@
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>CVE-2026-21441</t>
+          <t>GHSA-wqvq-5m8c-6g24</t>
         </is>
       </c>
       <c r="C46" s="31" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>ghsa</t>
+          <t>github-language-python</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>urllib3 is an HTTP client library for Python. urllib3's streaming API is designed for the efficient handling of large HT</t>
+          <t>CRLF injection in urllib3</t>
         </is>
       </c>
       <c r="F46" s="20" t="inlineStr">
@@ -3960,7 +3959,7 @@
       </c>
       <c r="H46" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+          <t>https://github.com/advisories/GHSA-wqvq-5m8c-6g24</t>
         </is>
       </c>
     </row>
@@ -3970,10 +3969,10 @@
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>CVE-2026-25645</t>
-        </is>
-      </c>
-      <c r="C47" s="30" t="inlineStr">
+          <t>CVE-2018-16984</t>
+        </is>
+      </c>
+      <c r="C47" s="31" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -3985,12 +3984,12 @@
       </c>
       <c r="E47" s="23" t="inlineStr">
         <is>
-          <t>Requests is a HTTP library. Prior to version 2.33.0, the `requests.utils.extract_zipped_paths()` utility function uses a</t>
+          <t>An issue was discovered in Django 2.1 before 2.1.2, in which unprivileged users can read the password hashes of arbitrar</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t>requests</t>
+          <t>django</t>
         </is>
       </c>
       <c r="G47" s="22" t="inlineStr">
@@ -4010,35 +4009,1757 @@
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
+          <t>CVE-2019-10906</t>
+        </is>
+      </c>
+      <c r="C48" s="30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>In Pallets Jinja before 2.10.1, str.format_map allows a sandbox escape.</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>jinja2</t>
+        </is>
+      </c>
+      <c r="G48" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H48" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="22" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2019-11236</t>
+        </is>
+      </c>
+      <c r="C49" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="inlineStr">
+        <is>
+          <t>In the urllib3 library through 1.24.1 for Python, CRLF injection is possible if the attacker controls the request parame</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="inlineStr">
+        <is>
+          <t>urllib3</t>
+        </is>
+      </c>
+      <c r="G49" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H49" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="19" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2019-11358</t>
+        </is>
+      </c>
+      <c r="C50" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>jQuery before 3.4.0, as used in Drupal, Backdrop CMS, and other products, mishandles jQuery.extend(true, {}, ...) becaus</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G50" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H50" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="22" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2019-12308</t>
+        </is>
+      </c>
+      <c r="C51" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="inlineStr">
+        <is>
+          <t>An issue was discovered in Django 1.11 before 1.11.21, 2.1 before 2.1.9, and 2.2 before 2.2.2. The clickable Current URL</t>
+        </is>
+      </c>
+      <c r="F51" s="23" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H51" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="19" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2019-12781</t>
+        </is>
+      </c>
+      <c r="C52" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>An issue was discovered in Django 1.11 before 1.11.22, 2.1 before 2.1.10, and 2.2 before 2.2.3. An HTTP request is not r</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G52" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2019-14232</t>
+        </is>
+      </c>
+      <c r="C53" s="30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E53" s="23" t="inlineStr">
+        <is>
+          <t>An issue was discovered in Django 1.11.x before 1.11.23, 2.1.x before 2.1.11, and 2.2.x before 2.2.4. If django.utils.te</t>
+        </is>
+      </c>
+      <c r="F53" s="23" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H53" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="19" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2019-14233</t>
+        </is>
+      </c>
+      <c r="C54" s="30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E54" s="20" t="inlineStr">
+        <is>
+          <t>An issue was discovered in Django 1.11.x before 1.11.23, 2.1.x before 2.1.11, and 2.2.x before 2.2.4. Due to the behavio</t>
+        </is>
+      </c>
+      <c r="F54" s="20" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G54" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H54" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="22" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2019-14234</t>
+        </is>
+      </c>
+      <c r="C55" s="32" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
+          <t>An issue was discovered in Django 1.11.x before 1.11.23, 2.1.x before 2.1.11, and 2.2.x before 2.2.4. Due to an error in</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H55" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="19" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2019-14235</t>
+        </is>
+      </c>
+      <c r="C56" s="30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E56" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An issue was discovered in Django 1.11.x before 1.11.23, 2.1.x before 2.1.11, and 2.2.x before 2.2.4. If passed certain </t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G56" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H56" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="22" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2019-19118</t>
+        </is>
+      </c>
+      <c r="C57" s="30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E57" s="23" t="inlineStr">
+        <is>
+          <t>Django 2.1 before 2.1.15 and 2.2 before 2.2.8 allows unintended model editing. A Django model admin displaying inline re</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H57" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="19" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2019-19844</t>
+        </is>
+      </c>
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E58" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Django before 1.11.27, 2.x before 2.2.9, and 3.x before 3.0.1 allows account takeover. A suitably crafted email address </t>
+        </is>
+      </c>
+      <c r="F58" s="20" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G58" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H58" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="22" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2019-3498</t>
+        </is>
+      </c>
+      <c r="C59" s="30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E59" s="23" t="inlineStr">
+        <is>
+          <t>In Django 1.11.x before 1.11.18, 2.0.x before 2.0.10, and 2.1.x before 2.1.5, an Improper Neutralization of Special Elem</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G59" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H59" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="19" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2019-6446</t>
+        </is>
+      </c>
+      <c r="C60" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D60" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E60" s="20" t="inlineStr">
+        <is>
+          <t>An issue was discovered in NumPy before 1.16.3. It uses the pickle Python module unsafely, which allows remote attackers</t>
+        </is>
+      </c>
+      <c r="F60" s="20" t="inlineStr">
+        <is>
+          <t>numpy</t>
+        </is>
+      </c>
+      <c r="G60" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H60" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="22" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2019-6975</t>
+        </is>
+      </c>
+      <c r="C61" s="30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D61" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E61" s="23" t="inlineStr">
+        <is>
+          <t>Django 1.11.x before 1.11.19, 2.0.x before 2.0.11, and 2.1.x before 2.1.6 allows Uncontrolled Memory Consumption via a m</t>
+        </is>
+      </c>
+      <c r="F61" s="23" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G61" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H61" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="19" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2020-26137</t>
+        </is>
+      </c>
+      <c r="C62" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D62" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E62" s="20" t="inlineStr">
+        <is>
+          <t>urllib3 before 1.25.9 allows CRLF injection if the attacker controls the HTTP request method, as demonstrated by inserti</t>
+        </is>
+      </c>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>urllib3</t>
+        </is>
+      </c>
+      <c r="G62" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H62" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="22" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2020-28493</t>
+        </is>
+      </c>
+      <c r="C63" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D63" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E63" s="23" t="inlineStr">
+        <is>
+          <t>This affects the package jinja2 from 0.0.0 and before 2.11.3. The ReDoS vulnerability is mainly due to the `_punctuation</t>
+        </is>
+      </c>
+      <c r="F63" s="23" t="inlineStr">
+        <is>
+          <t>jinja2</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H63" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="19" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2020-7471</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="D64" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E64" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Django 1.11 before 1.11.28, 2.2 before 2.2.10, and 3.0 before 3.0.3 allows SQL Injection if untrusted data is used as a </t>
+        </is>
+      </c>
+      <c r="F64" s="20" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G64" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H64" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="22" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2021-33203</t>
+        </is>
+      </c>
+      <c r="C65" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D65" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E65" s="23" t="inlineStr">
+        <is>
+          <t>Django before 2.2.24, 3.x before 3.1.12, and 3.2.x before 3.2.4 has a potential directory traversal via django.contrib.a</t>
+        </is>
+      </c>
+      <c r="F65" s="23" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H65" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="19" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2021-33430</t>
+        </is>
+      </c>
+      <c r="C66" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D66" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E66" s="20" t="inlineStr">
+        <is>
+          <t>A Buffer Overflow vulnerability exists in NumPy 1.9.x in the PyArray_NewFromDescr_int function of ctors.c when specifyin</t>
+        </is>
+      </c>
+      <c r="F66" s="20" t="inlineStr">
+        <is>
+          <t>numpy</t>
+        </is>
+      </c>
+      <c r="G66" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H66" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="22" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2021-34141</t>
+        </is>
+      </c>
+      <c r="C67" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D67" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E67" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An incomplete string comparison in the numpy.core component in NumPy before 1.22.0 allows attackers to trigger slightly </t>
+        </is>
+      </c>
+      <c r="F67" s="23" t="inlineStr">
+        <is>
+          <t>numpy</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H67" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="19" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2021-41495</t>
+        </is>
+      </c>
+      <c r="C68" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D68" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E68" s="20" t="inlineStr">
+        <is>
+          <t>Null Pointer Dereference vulnerability exists in numpy.sort in NumPy &amp;lt and 1.19 in the PyArray_DescrNew function due t</t>
+        </is>
+      </c>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>numpy</t>
+        </is>
+      </c>
+      <c r="G68" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H68" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="22" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2021-41496</t>
+        </is>
+      </c>
+      <c r="C69" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D69" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E69" s="23" t="inlineStr">
+        <is>
+          <t>Buffer overflow in the array_from_pyobj function of fortranobject.c in NumPy &lt; 1.19, which allows attackers to conduct a</t>
+        </is>
+      </c>
+      <c r="F69" s="23" t="inlineStr">
+        <is>
+          <t>numpy</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H69" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="19" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2022-36359</t>
+        </is>
+      </c>
+      <c r="C70" s="30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D70" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E70" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An issue was discovered in the HTTP FileResponse class in Django 3.2 before 3.2.15 and 4.0 before 4.0.7. An application </t>
+        </is>
+      </c>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G70" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H70" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="22" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2023-32681</t>
+        </is>
+      </c>
+      <c r="C71" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D71" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E71" s="23" t="inlineStr">
+        <is>
+          <t>Requests is a HTTP library. Since Requests 2.3.0, Requests has been leaking Proxy-Authorization headers to destination s</t>
+        </is>
+      </c>
+      <c r="F71" s="23" t="inlineStr">
+        <is>
+          <t>requests</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H71" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="19" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2023-43804</t>
+        </is>
+      </c>
+      <c r="C72" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D72" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E72" s="20" t="inlineStr">
+        <is>
+          <t>urllib3 is a user-friendly HTTP client library for Python. urllib3 doesn't treat the `Cookie` HTTP header special or pro</t>
+        </is>
+      </c>
+      <c r="F72" s="20" t="inlineStr">
+        <is>
+          <t>urllib3</t>
+        </is>
+      </c>
+      <c r="G72" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H72" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="22" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2023-45803</t>
+        </is>
+      </c>
+      <c r="C73" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D73" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E73" s="23" t="inlineStr">
+        <is>
+          <t>urllib3 is a user-friendly HTTP client library for Python. urllib3 previously wouldn't remove the HTTP request body when</t>
+        </is>
+      </c>
+      <c r="F73" s="23" t="inlineStr">
+        <is>
+          <t>urllib3</t>
+        </is>
+      </c>
+      <c r="G73" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H73" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="19" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2024-22195</t>
+        </is>
+      </c>
+      <c r="C74" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D74" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E74" s="20" t="inlineStr">
+        <is>
+          <t>Jinja is an extensible templating engine. Special placeholders in the template allow writing code similar to Python synt</t>
+        </is>
+      </c>
+      <c r="F74" s="20" t="inlineStr">
+        <is>
+          <t>jinja2</t>
+        </is>
+      </c>
+      <c r="G74" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H74" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="22" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2024-34064</t>
+        </is>
+      </c>
+      <c r="C75" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D75" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E75" s="23" t="inlineStr">
+        <is>
+          <t>Jinja is an extensible templating engine. The `xmlattr` filter in affected versions of Jinja accepts keys containing non</t>
+        </is>
+      </c>
+      <c r="F75" s="23" t="inlineStr">
+        <is>
+          <t>jinja2</t>
+        </is>
+      </c>
+      <c r="G75" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H75" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="19" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2024-35195</t>
+        </is>
+      </c>
+      <c r="C76" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D76" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E76" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Requests is a HTTP library. Prior to 2.32.0, when making requests through a Requests `Session`, if the first request is </t>
+        </is>
+      </c>
+      <c r="F76" s="20" t="inlineStr">
+        <is>
+          <t>requests</t>
+        </is>
+      </c>
+      <c r="G76" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H76" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="22" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2024-37891</t>
+        </is>
+      </c>
+      <c r="C77" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D77" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E77" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> urllib3 is a user-friendly HTTP client library for Python. When using urllib3's proxy support with `ProxyManager`, the </t>
+        </is>
+      </c>
+      <c r="F77" s="23" t="inlineStr">
+        <is>
+          <t>urllib3</t>
+        </is>
+      </c>
+      <c r="G77" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H77" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="19" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2024-45231</t>
+        </is>
+      </c>
+      <c r="C78" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D78" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E78" s="20" t="inlineStr">
+        <is>
+          <t>An issue was discovered in Django v5.1.1, v5.0.9, and v4.2.16. The django.contrib.auth.forms.PasswordResetForm class, wh</t>
+        </is>
+      </c>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G78" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H78" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="22" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2024-47081</t>
+        </is>
+      </c>
+      <c r="C79" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D79" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E79" s="23" t="inlineStr">
+        <is>
+          <t>Requests is a HTTP library. Due to a URL parsing issue, Requests releases prior to 2.32.4 may leak .netrc credentials to</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr">
+        <is>
+          <t>requests</t>
+        </is>
+      </c>
+      <c r="G79" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H79" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="19" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2024-56326</t>
+        </is>
+      </c>
+      <c r="C80" s="30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D80" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E80" s="20" t="inlineStr">
+        <is>
+          <t>Jinja is an extensible templating engine. Prior to 3.1.5, An oversight in how the Jinja sandboxed environment detects ca</t>
+        </is>
+      </c>
+      <c r="F80" s="20" t="inlineStr">
+        <is>
+          <t>jinja2</t>
+        </is>
+      </c>
+      <c r="G80" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H80" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="22" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2025-27516</t>
+        </is>
+      </c>
+      <c r="C81" s="30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D81" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E81" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jinja is an extensible templating engine. Prior to 3.1.6, an oversight in how the Jinja sandboxed environment interacts </t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr">
+        <is>
+          <t>jinja2</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H81" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="19" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2025-48432</t>
+        </is>
+      </c>
+      <c r="C82" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D82" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E82" s="20" t="inlineStr">
+        <is>
+          <t>An issue was discovered in Django 5.2 before 5.2.3, 5.1 before 5.1.11, and 4.2 before 4.2.23. Internal HTTP response log</t>
+        </is>
+      </c>
+      <c r="F82" s="20" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G82" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H82" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="22" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2025-50181</t>
+        </is>
+      </c>
+      <c r="C83" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D83" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E83" s="23" t="inlineStr">
+        <is>
+          <t>urllib3 is a user-friendly HTTP client library for Python. Prior to 2.5.0, it is possible to disable redirects for all r</t>
+        </is>
+      </c>
+      <c r="F83" s="23" t="inlineStr">
+        <is>
+          <t>urllib3</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H83" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="19" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2025-57833</t>
+        </is>
+      </c>
+      <c r="C84" s="30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E84" s="20" t="inlineStr">
+        <is>
+          <t>An issue was discovered in Django 4.2 before 4.2.24, 5.1 before 5.1.12, and 5.2 before 5.2.6. FilteredRelation is subjec</t>
+        </is>
+      </c>
+      <c r="F84" s="20" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G84" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H84" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="22" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2025-64458</t>
+        </is>
+      </c>
+      <c r="C85" s="30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D85" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E85" s="23" t="inlineStr">
+        <is>
+          <t>An issue was discovered in 5.1 before 5.1.14, 4.2 before 4.2.26, and 5.2 before 5.2.8.
+NFKC normalization in Python is s</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H85" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="19" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2025-64459</t>
+        </is>
+      </c>
+      <c r="C86" s="32" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="D86" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E86" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An issue was discovered in 5.1 before 5.1.14, 4.2 before 4.2.26, and 5.2 before 5.2.8.
+The methods `QuerySet.filter()`, </t>
+        </is>
+      </c>
+      <c r="F86" s="20" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="G86" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H86" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="22" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2025-66418</t>
+        </is>
+      </c>
+      <c r="C87" s="30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D87" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E87" s="23" t="inlineStr">
+        <is>
+          <t>urllib3 is a user-friendly HTTP client library for Python. Starting in version 1.24 and prior to 2.6.0, the number of li</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>urllib3</t>
+        </is>
+      </c>
+      <c r="G87" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H87" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="19" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2025-66471</t>
+        </is>
+      </c>
+      <c r="C88" s="30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D88" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E88" s="20" t="inlineStr">
+        <is>
+          <t>urllib3 is a user-friendly HTTP client library for Python. Starting in version 1.0 and prior to 2.6.0, the Streaming API</t>
+        </is>
+      </c>
+      <c r="F88" s="20" t="inlineStr">
+        <is>
+          <t>urllib3</t>
+        </is>
+      </c>
+      <c r="G88" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H88" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="22" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="23" t="inlineStr">
+        <is>
+          <t>CVE-2026-21441</t>
+        </is>
+      </c>
+      <c r="C89" s="30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D89" s="23" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E89" s="23" t="inlineStr">
+        <is>
+          <t>urllib3 is an HTTP client library for Python. urllib3's streaming API is designed for the efficient handling of large HT</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr">
+        <is>
+          <t>urllib3</t>
+        </is>
+      </c>
+      <c r="G89" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H89" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="19" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" s="20" t="inlineStr">
+        <is>
+          <t>CVE-2026-25645</t>
+        </is>
+      </c>
+      <c r="C90" s="31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D90" s="20" t="inlineStr">
+        <is>
+          <t>ghsa</t>
+        </is>
+      </c>
+      <c r="E90" s="20" t="inlineStr">
+        <is>
+          <t>Requests is a HTTP library. Prior to version 2.33.0, the `requests.utils.extract_zipped_paths()` utility function uses a</t>
+        </is>
+      </c>
+      <c r="F90" s="20" t="inlineStr">
+        <is>
+          <t>requests</t>
+        </is>
+      </c>
+      <c r="G90" s="19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H90" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="22" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" s="23" t="inlineStr">
+        <is>
           <t>CVE-2026-44431</t>
         </is>
       </c>
-      <c r="C48" s="31" t="inlineStr">
+      <c r="C91" s="30" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D48" s="20" t="inlineStr">
+      <c r="D91" s="23" t="inlineStr">
         <is>
           <t>ghsa</t>
         </is>
       </c>
-      <c r="E48" s="20" t="inlineStr">
+      <c r="E91" s="23" t="inlineStr">
         <is>
           <t>urllib3 is an HTTP client library for Python. From 1.23 to before 2.7.0, cross-origin redirects followed from the low-le</t>
         </is>
       </c>
-      <c r="F48" s="20" t="inlineStr">
+      <c r="F91" s="23" t="inlineStr">
         <is>
           <t>urllib3</t>
         </is>
       </c>
-      <c r="G48" s="19" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="H48" s="20" t="inlineStr">
+      <c r="G91" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H91" s="23" t="inlineStr">
         <is>
           <t>https://github.com/advisories?query=type%3Areviewed+ecosystem%3Apip</t>
         </is>

--- a/sbom_output/public/sbom_report.xlsx
+++ b/sbom_output/public/sbom_report.xlsx
@@ -726,7 +726,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CycloneDX v1.5 | Generated: 2026-06-29T08:32:21Z | Report Date: 2026-06-29 14:02</t>
+          <t>CycloneDX v1.5 | Generated: 2026-06-29T09:42:44Z | Report Date: 2026-06-29 15:12</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Author: Client-Assigned Scanning Service  |  Generated: 2026-06-29T08:32:21Z</t>
+          <t>Author: Client-Assigned Scanning Service  |  Generated: 2026-06-29T09:42:44Z</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="S5" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29T08:32:21Z</t>
+          <t>2026-06-29T09:42:44Z</t>
         </is>
       </c>
       <c r="T5" s="20" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="S6" s="23" t="inlineStr">
         <is>
-          <t>2026-06-29T08:32:21Z</t>
+          <t>2026-06-29T09:42:44Z</t>
         </is>
       </c>
       <c r="T6" s="23" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="S7" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29T08:32:21Z</t>
+          <t>2026-06-29T09:42:44Z</t>
         </is>
       </c>
       <c r="T7" s="20" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="S8" s="23" t="inlineStr">
         <is>
-          <t>2026-06-29T08:32:21Z</t>
+          <t>2026-06-29T09:42:44Z</t>
         </is>
       </c>
       <c r="T8" s="23" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="S9" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29T08:32:21Z</t>
+          <t>2026-06-29T09:42:44Z</t>
         </is>
       </c>
       <c r="T9" s="20" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t>jinja2, urllib3, requests, numpy, django</t>
+          <t>jinja2, numpy, urllib3, requests, django</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="K10" s="22" t="inlineStr">
         <is>
-          <t>2026-06-29T08:32:22.033242Z</t>
+          <t>2026-06-29T09:42:47.425391Z</t>
         </is>
       </c>
       <c r="L10" s="22" t="inlineStr">
         <is>
-          <t>2029-06-28T08:32:22Z</t>
+          <t>2029-06-28T09:42:47Z</t>
         </is>
       </c>
       <c r="M10" s="26" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="S10" s="23" t="inlineStr">
         <is>
-          <t>2026-06-29T08:32:21Z</t>
+          <t>2026-06-29T09:42:44Z</t>
         </is>
       </c>
       <c r="T10" s="23" t="inlineStr">

--- a/sbom_output/public/sbom_report.xlsx
+++ b/sbom_output/public/sbom_report.xlsx
@@ -723,7 +723,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CycloneDX v1.5 | Generated: 2026-06-30T09:11:07Z | Report Date: 2026-06-30 14:41</t>
+          <t>CycloneDX v1.5 | Generated: 2026-06-30T09:47:46Z | Report Date: 2026-06-30 15:17</t>
         </is>
       </c>
     </row>
@@ -1061,9 +1061,9 @@
     <col width="35" customWidth="1" min="18" max="18"/>
     <col width="23" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
-    <col width="37" customWidth="1" min="21" max="21"/>
+    <col width="29" customWidth="1" min="21" max="21"/>
     <col width="19" customWidth="1" min="22" max="22"/>
-    <col width="31" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
     <col width="27" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="45" customWidth="1" min="26" max="26"/>
@@ -1082,7 +1082,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Author: Client-Assigned Scanning Service  |  Generated: 2026-06-30T09:11:07Z</t>
+          <t>Author: Client-Assigned Scanning Service  |  Generated: 2026-06-30T09:47:46Z</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
-          <t>open-source</t>
+          <t>Open-Source</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="S5" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30T09:11:07Z</t>
+          <t>2026-06-30T09:47:46Z</t>
         </is>
       </c>
       <c r="T5" s="20" t="inlineStr">
@@ -1335,17 +1335,17 @@
       </c>
       <c r="U5" s="19" t="inlineStr">
         <is>
-          <t>PyPI package (typically a library)</t>
+          <t>pkg:pypi ecosystem package</t>
         </is>
       </c>
       <c r="V5" s="19" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="W5" s="20" t="inlineStr">
         <is>
-          <t>CycloneDX JSON v1.6 (Merged)</t>
+          <t>true</t>
         </is>
       </c>
       <c r="X5" s="19" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>open-source</t>
+          <t>Open-Source</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="S6" s="23" t="inlineStr">
         <is>
-          <t>2026-06-30T09:11:07Z</t>
+          <t>2026-06-30T09:47:46Z</t>
         </is>
       </c>
       <c r="T6" s="23" t="inlineStr">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="U6" s="22" t="inlineStr">
         <is>
-          <t>PyPI package (typically a library)</t>
+          <t>pkg:pypi ecosystem package</t>
         </is>
       </c>
       <c r="V6" s="22" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="W6" s="23" t="inlineStr">
         <is>
-          <t>CycloneDX JSON v1.6 (Merged)</t>
+          <t>true</t>
         </is>
       </c>
       <c r="X6" s="22" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>open-source</t>
+          <t>Open-Source</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="S7" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30T09:11:07Z</t>
+          <t>2026-06-30T09:47:46Z</t>
         </is>
       </c>
       <c r="T7" s="20" t="inlineStr">
@@ -1633,17 +1633,17 @@
       </c>
       <c r="U7" s="19" t="inlineStr">
         <is>
-          <t>PyPI package (typically a library)</t>
+          <t>pkg:pypi ecosystem package</t>
         </is>
       </c>
       <c r="V7" s="19" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="W7" s="20" t="inlineStr">
         <is>
-          <t>CycloneDX JSON v1.6 (Merged)</t>
+          <t>true</t>
         </is>
       </c>
       <c r="X7" s="19" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>open-source</t>
+          <t>Open-Source</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="S8" s="23" t="inlineStr">
         <is>
-          <t>2026-06-30T09:11:07Z</t>
+          <t>2026-06-30T09:47:46Z</t>
         </is>
       </c>
       <c r="T8" s="23" t="inlineStr">
@@ -1782,17 +1782,17 @@
       </c>
       <c r="U8" s="22" t="inlineStr">
         <is>
-          <t>PyPI package (typically a library)</t>
+          <t>pkg:pypi ecosystem package</t>
         </is>
       </c>
       <c r="V8" s="22" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="W8" s="23" t="inlineStr">
         <is>
-          <t>CycloneDX JSON v1.6 (Merged)</t>
+          <t>true</t>
         </is>
       </c>
       <c r="X8" s="22" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G9" s="20" t="inlineStr">
         <is>
-          <t>open-source</t>
+          <t>Open-Source</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="S9" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30T09:11:07Z</t>
+          <t>2026-06-30T09:47:46Z</t>
         </is>
       </c>
       <c r="T9" s="20" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="U9" s="19" t="inlineStr">
         <is>
-          <t>PyPI package (typically a library)</t>
+          <t>pkg:pypi ecosystem package</t>
         </is>
       </c>
       <c r="V9" s="19" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="W9" s="20" t="inlineStr">
         <is>
-          <t>CycloneDX JSON v1.6 (Merged)</t>
+          <t>true</t>
         </is>
       </c>
       <c r="X9" s="19" t="inlineStr">
